--- a/AAII_Financials/Quarterly/TOFB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TOFB_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,176 +656,180 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45108</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45017</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44835</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44744</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44653</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44562</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44471</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44380</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44289</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44198</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44100</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44009</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43918</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43827</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43736</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43645</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43554</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43463</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43372</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43099</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42917</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42826</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E8" s="3">
         <v>2700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4200</v>
-      </c>
-      <c r="O8" s="3">
-        <v>3200</v>
       </c>
       <c r="P8" s="3">
         <v>3200</v>
@@ -834,227 +838,236 @@
         <v>3200</v>
       </c>
       <c r="R8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="S8" s="3">
         <v>3400</v>
-      </c>
-      <c r="S8" s="3">
-        <v>3100</v>
       </c>
       <c r="T8" s="3">
         <v>3100</v>
       </c>
       <c r="U8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="V8" s="3">
         <v>3500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3300</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>3600</v>
       </c>
       <c r="AE8" s="3">
         <v>3600</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E9" s="3">
         <v>2100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3000</v>
-      </c>
-      <c r="G9" s="3">
-        <v>2500</v>
       </c>
       <c r="H9" s="3">
         <v>2500</v>
       </c>
       <c r="I9" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J9" s="3">
         <v>2600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2100</v>
-      </c>
-      <c r="P9" s="3">
-        <v>2200</v>
       </c>
       <c r="Q9" s="3">
         <v>2200</v>
       </c>
       <c r="R9" s="3">
+        <v>2200</v>
+      </c>
+      <c r="S9" s="3">
         <v>2100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2500</v>
-      </c>
-      <c r="V9" s="3">
-        <v>2000</v>
       </c>
       <c r="W9" s="3">
         <v>2000</v>
       </c>
       <c r="X9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Y9" s="3">
         <v>2400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2300</v>
-      </c>
-      <c r="AD9" s="3">
-        <v>2500</v>
       </c>
       <c r="AE9" s="3">
         <v>2500</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E10" s="3">
         <v>600</v>
       </c>
       <c r="F10" s="3">
+        <v>600</v>
+      </c>
+      <c r="G10" s="3">
         <v>500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1100</v>
-      </c>
-      <c r="P10" s="3">
-        <v>1000</v>
       </c>
       <c r="Q10" s="3">
         <v>1000</v>
       </c>
       <c r="R10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S10" s="3">
         <v>1300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>800</v>
-      </c>
-      <c r="U10" s="3">
-        <v>1000</v>
       </c>
       <c r="V10" s="3">
         <v>1000</v>
       </c>
       <c r="W10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X10" s="3">
         <v>800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1000</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>1300</v>
       </c>
       <c r="Z10" s="3">
         <v>1300</v>
       </c>
       <c r="AA10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AB10" s="3">
         <v>1200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1000</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>1100</v>
       </c>
       <c r="AE10" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1086,16 +1099,17 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F12" s="3">
         <v>0</v>
@@ -1125,7 +1139,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P12" s="3">
         <v>100</v>
@@ -1175,8 +1189,11 @@
       <c r="AE12" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1264,8 +1281,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1285,10 +1305,10 @@
         <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-200</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>24</v>
@@ -1302,8 +1322,8 @@
       <c r="N14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1353,8 +1373,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1442,8 +1465,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1472,52 +1498,53 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E17" s="3">
         <v>2900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3200</v>
-      </c>
-      <c r="L17" s="3">
-        <v>3000</v>
       </c>
       <c r="M17" s="3">
         <v>3000</v>
       </c>
       <c r="N17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="O17" s="3">
         <v>3800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3000</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>3200</v>
       </c>
       <c r="R17" s="3">
         <v>3200</v>
@@ -1529,129 +1556,135 @@
         <v>3200</v>
       </c>
       <c r="U17" s="3">
+        <v>3200</v>
+      </c>
+      <c r="V17" s="3">
         <v>3500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3000</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>3400</v>
       </c>
       <c r="AC17" s="3">
         <v>3400</v>
       </c>
       <c r="AD17" s="3">
+        <v>3400</v>
+      </c>
+      <c r="AE17" s="3">
         <v>3500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-400</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-300</v>
       </c>
       <c r="H18" s="3">
         <v>-300</v>
       </c>
       <c r="I18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J18" s="3">
         <v>300</v>
       </c>
-      <c r="J18" s="3">
-        <v>0</v>
-      </c>
       <c r="K18" s="3">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
         <v>200</v>
       </c>
-      <c r="L18" s="3">
-        <v>0</v>
-      </c>
       <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
         <v>200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>200</v>
       </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
       <c r="R18" s="3">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3">
         <v>200</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-100</v>
       </c>
       <c r="T18" s="3">
         <v>-100</v>
       </c>
       <c r="U18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V18" s="3">
         <v>0</v>
       </c>
       <c r="W18" s="3">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3">
         <v>-100</v>
       </c>
-      <c r="X18" s="3">
-        <v>100</v>
-      </c>
       <c r="Y18" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="Z18" s="3">
         <v>400</v>
       </c>
       <c r="AA18" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB18" s="3">
         <v>300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-100</v>
       </c>
-      <c r="AD18" s="3">
-        <v>100</v>
-      </c>
       <c r="AE18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1683,8 +1716,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1716,11 +1750,11 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1772,76 +1806,79 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-400</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-300</v>
       </c>
       <c r="H21" s="3">
         <v>-300</v>
       </c>
       <c r="I21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J21" s="3">
         <v>200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-100</v>
       </c>
-      <c r="K21" s="3">
-        <v>100</v>
-      </c>
       <c r="L21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N21" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="O21" s="3">
         <v>300</v>
       </c>
       <c r="P21" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q21" s="3">
         <v>200</v>
       </c>
-      <c r="Q21" s="3">
-        <v>100</v>
-      </c>
       <c r="R21" s="3">
+        <v>100</v>
+      </c>
+      <c r="S21" s="3">
         <v>200</v>
       </c>
-      <c r="S21" s="3">
-        <v>0</v>
-      </c>
       <c r="T21" s="3">
+        <v>0</v>
+      </c>
+      <c r="U21" s="3">
         <v>-100</v>
       </c>
-      <c r="U21" s="3">
-        <v>0</v>
-      </c>
       <c r="V21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W21" s="3">
+        <v>100</v>
+      </c>
+      <c r="X21" s="3">
         <v>-100</v>
       </c>
-      <c r="X21" s="3">
-        <v>100</v>
-      </c>
       <c r="Y21" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Z21" s="3">
         <v>300</v>
@@ -1853,16 +1890,19 @@
         <v>300</v>
       </c>
       <c r="AC21" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-200</v>
       </c>
-      <c r="AD21" s="3">
-        <v>100</v>
-      </c>
       <c r="AE21" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1950,76 +1990,79 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-400</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-300</v>
       </c>
       <c r="H23" s="3">
         <v>-300</v>
       </c>
       <c r="I23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J23" s="3">
         <v>200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-100</v>
       </c>
-      <c r="K23" s="3">
-        <v>100</v>
-      </c>
       <c r="L23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N23" s="3">
+        <v>100</v>
+      </c>
+      <c r="O23" s="3">
         <v>300</v>
-      </c>
-      <c r="O23" s="3">
-        <v>200</v>
       </c>
       <c r="P23" s="3">
         <v>200</v>
       </c>
       <c r="Q23" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R23" s="3">
+        <v>100</v>
+      </c>
+      <c r="S23" s="3">
         <v>200</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
       <c r="T23" s="3">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
       <c r="V23" s="3">
         <v>0</v>
       </c>
       <c r="W23" s="3">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3">
         <v>-100</v>
       </c>
-      <c r="X23" s="3">
-        <v>100</v>
-      </c>
       <c r="Y23" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Z23" s="3">
         <v>300</v>
@@ -2031,27 +2074,30 @@
         <v>300</v>
       </c>
       <c r="AC23" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD23" s="3">
         <v>-200</v>
       </c>
-      <c r="AD23" s="3">
-        <v>100</v>
-      </c>
       <c r="AE23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G24" s="3">
         <v>-100</v>
@@ -2060,7 +2106,7 @@
         <v>-100</v>
       </c>
       <c r="I24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J24" s="3">
         <v>0</v>
@@ -2075,16 +2121,16 @@
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -2099,11 +2145,11 @@
         <v>0</v>
       </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>-200</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
         <v>0</v>
       </c>
@@ -2111,11 +2157,11 @@
         <v>0</v>
       </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-100</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
       <c r="AB24" s="3">
         <v>0</v>
       </c>
@@ -2128,8 +2174,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2217,186 +2266,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-300</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-200</v>
       </c>
       <c r="H26" s="3">
         <v>-200</v>
       </c>
       <c r="I26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J26" s="3">
         <v>200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-100</v>
       </c>
-      <c r="K26" s="3">
-        <v>100</v>
-      </c>
       <c r="L26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N26" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O26" s="3">
         <v>200</v>
       </c>
       <c r="P26" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q26" s="3">
         <v>100</v>
       </c>
       <c r="R26" s="3">
+        <v>100</v>
+      </c>
+      <c r="S26" s="3">
         <v>200</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
       <c r="T26" s="3">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
         <v>-100</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
       <c r="V26" s="3">
+        <v>0</v>
+      </c>
+      <c r="W26" s="3">
         <v>200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-100</v>
       </c>
-      <c r="X26" s="3">
-        <v>100</v>
-      </c>
       <c r="Y26" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z26" s="3">
         <v>300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>400</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>300</v>
       </c>
       <c r="AB26" s="3">
         <v>300</v>
       </c>
       <c r="AC26" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD26" s="3">
         <v>-200</v>
       </c>
-      <c r="AD26" s="3">
-        <v>100</v>
-      </c>
       <c r="AE26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-300</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-200</v>
       </c>
       <c r="H27" s="3">
         <v>-200</v>
       </c>
       <c r="I27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J27" s="3">
         <v>200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-100</v>
       </c>
-      <c r="K27" s="3">
-        <v>100</v>
-      </c>
       <c r="L27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N27" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O27" s="3">
         <v>200</v>
       </c>
       <c r="P27" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q27" s="3">
         <v>100</v>
       </c>
       <c r="R27" s="3">
+        <v>100</v>
+      </c>
+      <c r="S27" s="3">
         <v>200</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3">
         <v>-100</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
       <c r="V27" s="3">
+        <v>0</v>
+      </c>
+      <c r="W27" s="3">
         <v>200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-100</v>
       </c>
-      <c r="X27" s="3">
-        <v>100</v>
-      </c>
       <c r="Y27" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z27" s="3">
         <v>300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>400</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>300</v>
       </c>
       <c r="AB27" s="3">
         <v>300</v>
       </c>
       <c r="AC27" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD27" s="3">
         <v>-200</v>
       </c>
-      <c r="AD27" s="3">
-        <v>100</v>
-      </c>
       <c r="AE27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2484,8 +2542,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2537,8 +2598,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>24</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>24</v>
@@ -2555,11 +2616,11 @@
       <c r="Y29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>24</v>
@@ -2573,8 +2634,11 @@
       <c r="AE29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2662,8 +2726,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2751,8 +2818,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2784,10 +2854,10 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
@@ -2840,76 +2910,79 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-300</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-200</v>
       </c>
       <c r="H33" s="3">
         <v>-200</v>
       </c>
       <c r="I33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J33" s="3">
         <v>200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-100</v>
       </c>
-      <c r="K33" s="3">
-        <v>100</v>
-      </c>
       <c r="L33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N33" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O33" s="3">
         <v>200</v>
       </c>
       <c r="P33" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q33" s="3">
         <v>100</v>
       </c>
       <c r="R33" s="3">
+        <v>100</v>
+      </c>
+      <c r="S33" s="3">
         <v>200</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3">
         <v>-100</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
       <c r="V33" s="3">
+        <v>0</v>
+      </c>
+      <c r="W33" s="3">
         <v>200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-100</v>
       </c>
-      <c r="X33" s="3">
-        <v>100</v>
-      </c>
       <c r="Y33" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Z33" s="3">
         <v>300</v>
@@ -2921,16 +2994,19 @@
         <v>300</v>
       </c>
       <c r="AC33" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD33" s="3">
         <v>-200</v>
       </c>
-      <c r="AD33" s="3">
-        <v>100</v>
-      </c>
       <c r="AE33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3018,76 +3094,79 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-300</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-200</v>
       </c>
       <c r="H35" s="3">
         <v>-200</v>
       </c>
       <c r="I35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J35" s="3">
         <v>200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-100</v>
       </c>
-      <c r="K35" s="3">
-        <v>100</v>
-      </c>
       <c r="L35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N35" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O35" s="3">
         <v>200</v>
       </c>
       <c r="P35" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q35" s="3">
         <v>100</v>
       </c>
       <c r="R35" s="3">
+        <v>100</v>
+      </c>
+      <c r="S35" s="3">
         <v>200</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
         <v>-100</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
       <c r="V35" s="3">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3">
         <v>200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-100</v>
       </c>
-      <c r="X35" s="3">
-        <v>100</v>
-      </c>
       <c r="Y35" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Z35" s="3">
         <v>300</v>
@@ -3099,110 +3178,116 @@
         <v>300</v>
       </c>
       <c r="AC35" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD35" s="3">
         <v>-200</v>
       </c>
-      <c r="AD35" s="3">
-        <v>100</v>
-      </c>
       <c r="AE35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45108</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45017</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44835</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44744</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44653</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44562</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44471</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44380</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44289</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44198</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44100</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44009</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43918</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43827</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43736</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43645</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43554</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43463</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43372</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43099</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42917</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42826</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3234,8 +3319,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3267,97 +3353,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>700</v>
+      </c>
+      <c r="E41" s="3">
         <v>600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>900</v>
-      </c>
-      <c r="R41" s="3">
-        <v>500</v>
       </c>
       <c r="S41" s="3">
         <v>500</v>
       </c>
       <c r="T41" s="3">
+        <v>500</v>
+      </c>
+      <c r="U41" s="3">
         <v>900</v>
-      </c>
-      <c r="U41" s="3">
-        <v>600</v>
       </c>
       <c r="V41" s="3">
         <v>600</v>
       </c>
       <c r="W41" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="X41" s="3">
         <v>500</v>
       </c>
       <c r="Y41" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z41" s="3">
         <v>800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>200</v>
       </c>
-      <c r="AD41" s="3">
-        <v>100</v>
-      </c>
       <c r="AE41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF41" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3445,126 +3535,132 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E43" s="3">
         <v>800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1300</v>
-      </c>
-      <c r="K43" s="3">
-        <v>1400</v>
       </c>
       <c r="L43" s="3">
         <v>1400</v>
       </c>
       <c r="M43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N43" s="3">
         <v>1300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2100</v>
-      </c>
-      <c r="O43" s="3">
-        <v>1600</v>
       </c>
       <c r="P43" s="3">
         <v>1600</v>
       </c>
       <c r="Q43" s="3">
+        <v>1600</v>
+      </c>
+      <c r="R43" s="3">
         <v>1300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E44" s="3">
         <v>2400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1700</v>
-      </c>
-      <c r="L44" s="3">
-        <v>2000</v>
       </c>
       <c r="M44" s="3">
         <v>2000</v>
@@ -3576,55 +3672,58 @@
         <v>2000</v>
       </c>
       <c r="P44" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Q44" s="3">
         <v>2100</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>1900</v>
       </c>
       <c r="R44" s="3">
         <v>1900</v>
       </c>
       <c r="S44" s="3">
+        <v>1900</v>
+      </c>
+      <c r="T44" s="3">
         <v>1800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1900</v>
-      </c>
-      <c r="X44" s="3">
-        <v>2000</v>
       </c>
       <c r="Y44" s="3">
         <v>2000</v>
       </c>
       <c r="Z44" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AA44" s="3">
         <v>1500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2000</v>
-      </c>
-      <c r="AD44" s="3">
-        <v>1600</v>
       </c>
       <c r="AE44" s="3">
         <v>1600</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3641,13 +3740,13 @@
         <v>100</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I45" s="3">
         <v>0</v>
       </c>
       <c r="J45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K45" s="3">
         <v>100</v>
@@ -3695,7 +3794,7 @@
         <v>100</v>
       </c>
       <c r="Z45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA45" s="3">
         <v>200</v>
@@ -3712,19 +3811,22 @@
       <c r="AE45" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E46" s="3">
         <v>3900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4000</v>
-      </c>
-      <c r="F46" s="3">
-        <v>4900</v>
       </c>
       <c r="G46" s="3">
         <v>4900</v>
@@ -3733,76 +3835,79 @@
         <v>4900</v>
       </c>
       <c r="I46" s="3">
+        <v>4900</v>
+      </c>
+      <c r="J46" s="3">
         <v>5400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4200</v>
-      </c>
-      <c r="AD46" s="3">
-        <v>4500</v>
       </c>
       <c r="AE46" s="3">
         <v>4500</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3890,13 +3995,16 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E48" s="3">
         <v>200</v>
@@ -3905,13 +4013,13 @@
         <v>200</v>
       </c>
       <c r="G48" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H48" s="3">
         <v>100</v>
       </c>
       <c r="I48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J48" s="3">
         <v>200</v>
@@ -3920,22 +4028,22 @@
         <v>200</v>
       </c>
       <c r="L48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M48" s="3">
         <v>300</v>
       </c>
       <c r="N48" s="3">
+        <v>300</v>
+      </c>
+      <c r="O48" s="3">
         <v>400</v>
-      </c>
-      <c r="O48" s="3">
-        <v>300</v>
       </c>
       <c r="P48" s="3">
         <v>300</v>
       </c>
       <c r="Q48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="R48" s="3">
         <v>400</v>
@@ -3944,19 +4052,19 @@
         <v>400</v>
       </c>
       <c r="T48" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="U48" s="3">
         <v>200</v>
       </c>
       <c r="V48" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W48" s="3">
         <v>100</v>
       </c>
       <c r="X48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y48" s="3">
         <v>0</v>
@@ -3979,8 +4087,11 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4068,8 +4179,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4157,8 +4271,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4246,8 +4363,11 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4255,20 +4375,20 @@
         <v>200</v>
       </c>
       <c r="E52" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F52" s="3">
         <v>400</v>
       </c>
       <c r="G52" s="3">
+        <v>400</v>
+      </c>
+      <c r="H52" s="3">
         <v>300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>200</v>
       </c>
-      <c r="I52" s="3">
-        <v>100</v>
-      </c>
       <c r="J52" s="3">
         <v>100</v>
       </c>
@@ -4285,32 +4405,32 @@
         <v>100</v>
       </c>
       <c r="O52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P52" s="3">
         <v>200</v>
       </c>
       <c r="Q52" s="3">
+        <v>200</v>
+      </c>
+      <c r="R52" s="3">
         <v>300</v>
-      </c>
-      <c r="R52" s="3">
-        <v>200</v>
       </c>
       <c r="S52" s="3">
         <v>200</v>
       </c>
       <c r="T52" s="3">
+        <v>200</v>
+      </c>
+      <c r="U52" s="3">
         <v>500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>200</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
-      </c>
       <c r="X52" s="3">
         <v>0</v>
       </c>
@@ -4335,8 +4455,11 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4424,97 +4547,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E54" s="3">
         <v>4300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5500</v>
-      </c>
-      <c r="G54" s="3">
-        <v>5300</v>
       </c>
       <c r="H54" s="3">
         <v>5300</v>
       </c>
       <c r="I54" s="3">
+        <v>5300</v>
+      </c>
+      <c r="J54" s="3">
         <v>5800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>4200</v>
-      </c>
-      <c r="AD54" s="3">
-        <v>4500</v>
       </c>
       <c r="AE54" s="3">
         <v>4500</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4546,8 +4675,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4579,97 +4709,101 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>500</v>
+      </c>
+      <c r="E57" s="3">
         <v>200</v>
       </c>
-      <c r="E57" s="3">
-        <v>100</v>
-      </c>
       <c r="F57" s="3">
+        <v>100</v>
+      </c>
+      <c r="G57" s="3">
         <v>700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3">
-        <v>100</v>
-      </c>
       <c r="K57" s="3">
+        <v>100</v>
+      </c>
+      <c r="L57" s="3">
         <v>800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>200</v>
-      </c>
-      <c r="O57" s="3">
-        <v>300</v>
       </c>
       <c r="P57" s="3">
         <v>300</v>
       </c>
       <c r="Q57" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3">
         <v>200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>400</v>
-      </c>
-      <c r="T57" s="3">
-        <v>600</v>
       </c>
       <c r="U57" s="3">
         <v>600</v>
       </c>
       <c r="V57" s="3">
+        <v>600</v>
+      </c>
+      <c r="W57" s="3">
         <v>400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>900</v>
-      </c>
-      <c r="AD57" s="3">
-        <v>1100</v>
       </c>
       <c r="AE57" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4692,7 +4826,7 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>200</v>
@@ -4701,19 +4835,19 @@
         <v>200</v>
       </c>
       <c r="M58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N58" s="3">
         <v>100</v>
       </c>
-      <c r="O58" s="3" t="s">
+      <c r="O58" s="3">
+        <v>100</v>
+      </c>
+      <c r="P58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P58" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>24</v>
+      <c r="Q58" s="3">
+        <v>100</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>24</v>
@@ -4727,8 +4861,8 @@
       <c r="U58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -4757,8 +4891,11 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4766,22 +4903,22 @@
         <v>300</v>
       </c>
       <c r="E59" s="3">
+        <v>300</v>
+      </c>
+      <c r="F59" s="3">
         <v>400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>500</v>
-      </c>
-      <c r="J59" s="3">
-        <v>400</v>
       </c>
       <c r="K59" s="3">
         <v>400</v>
@@ -4790,25 +4927,25 @@
         <v>400</v>
       </c>
       <c r="M59" s="3">
+        <v>400</v>
+      </c>
+      <c r="N59" s="3">
         <v>500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>700</v>
-      </c>
-      <c r="O59" s="3">
-        <v>300</v>
       </c>
       <c r="P59" s="3">
         <v>300</v>
       </c>
       <c r="Q59" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="R59" s="3">
         <v>400</v>
       </c>
       <c r="S59" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="T59" s="3">
         <v>300</v>
@@ -4820,123 +4957,129 @@
         <v>300</v>
       </c>
       <c r="W59" s="3">
+        <v>300</v>
+      </c>
+      <c r="X59" s="3">
         <v>200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>500</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>600</v>
       </c>
       <c r="AA59" s="3">
         <v>600</v>
       </c>
       <c r="AB59" s="3">
+        <v>600</v>
+      </c>
+      <c r="AC59" s="3">
         <v>500</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>400</v>
       </c>
       <c r="AD59" s="3">
         <v>400</v>
       </c>
       <c r="AE59" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF59" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="E60" s="3">
         <v>500</v>
       </c>
       <c r="F60" s="3">
+        <v>500</v>
+      </c>
+      <c r="G60" s="3">
         <v>1300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1000</v>
-      </c>
-      <c r="O60" s="3">
-        <v>700</v>
       </c>
       <c r="P60" s="3">
         <v>700</v>
       </c>
       <c r="Q60" s="3">
+        <v>700</v>
+      </c>
+      <c r="R60" s="3">
         <v>400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>800</v>
-      </c>
-      <c r="T60" s="3">
-        <v>900</v>
       </c>
       <c r="U60" s="3">
         <v>900</v>
       </c>
       <c r="V60" s="3">
+        <v>900</v>
+      </c>
+      <c r="W60" s="3">
         <v>600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4962,7 +5105,7 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="L61" s="3">
         <v>500</v>
@@ -4971,16 +5114,16 @@
         <v>500</v>
       </c>
       <c r="N61" s="3">
+        <v>500</v>
+      </c>
+      <c r="O61" s="3">
         <v>600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>600</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>500</v>
       </c>
       <c r="R61" s="3">
         <v>500</v>
@@ -5024,8 +5167,11 @@
       <c r="AE61" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5033,28 +5179,28 @@
         <v>0</v>
       </c>
       <c r="E62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F62" s="3">
         <v>100</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H62" s="3">
         <v>0</v>
       </c>
       <c r="I62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J62" s="3">
         <v>100</v>
       </c>
       <c r="K62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M62" s="3">
         <v>100</v>
@@ -5072,7 +5218,7 @@
         <v>100</v>
       </c>
       <c r="R62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S62" s="3">
         <v>200</v>
@@ -5083,8 +5229,8 @@
       <c r="U62" s="3">
         <v>200</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>24</v>
+      <c r="V62" s="3">
+        <v>200</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>24</v>
@@ -5095,8 +5241,8 @@
       <c r="Y62" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z62" s="3">
-        <v>0</v>
+      <c r="Z62" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AA62" s="3">
         <v>0</v>
@@ -5113,8 +5259,11 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5202,8 +5351,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5291,8 +5443,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5380,97 +5535,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="E66" s="3">
         <v>600</v>
       </c>
       <c r="F66" s="3">
+        <v>600</v>
+      </c>
+      <c r="G66" s="3">
         <v>1400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1700</v>
-      </c>
-      <c r="O66" s="3">
-        <v>1400</v>
       </c>
       <c r="P66" s="3">
         <v>1400</v>
       </c>
       <c r="Q66" s="3">
+        <v>1400</v>
+      </c>
+      <c r="R66" s="3">
         <v>1000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1400</v>
-      </c>
-      <c r="T66" s="3">
-        <v>1600</v>
       </c>
       <c r="U66" s="3">
         <v>1600</v>
       </c>
       <c r="V66" s="3">
+        <v>1600</v>
+      </c>
+      <c r="W66" s="3">
         <v>1100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1900</v>
-      </c>
-      <c r="AD66" s="3">
-        <v>2100</v>
       </c>
       <c r="AE66" s="3">
         <v>2100</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5502,8 +5663,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5591,8 +5753,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5680,8 +5845,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5769,8 +5937,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5858,61 +6029,64 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E72" s="3">
         <v>3400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4300</v>
-      </c>
-      <c r="M72" s="3">
-        <v>4200</v>
       </c>
       <c r="N72" s="3">
         <v>4200</v>
       </c>
       <c r="O72" s="3">
+        <v>4200</v>
+      </c>
+      <c r="P72" s="3">
         <v>4000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3800</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>3600</v>
       </c>
       <c r="R72" s="3">
         <v>3600</v>
       </c>
       <c r="S72" s="3">
+        <v>3600</v>
+      </c>
+      <c r="T72" s="3">
         <v>3400</v>
-      </c>
-      <c r="T72" s="3">
-        <v>3500</v>
       </c>
       <c r="U72" s="3">
         <v>3500</v>
@@ -5921,34 +6095,37 @@
         <v>3500</v>
       </c>
       <c r="W72" s="3">
+        <v>3500</v>
+      </c>
+      <c r="X72" s="3">
         <v>3300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>3000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6036,8 +6213,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6125,8 +6305,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6214,97 +6397,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E76" s="3">
         <v>3700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4700</v>
-      </c>
-      <c r="L76" s="3">
-        <v>4500</v>
       </c>
       <c r="M76" s="3">
         <v>4500</v>
       </c>
       <c r="N76" s="3">
+        <v>4500</v>
+      </c>
+      <c r="O76" s="3">
         <v>4400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3800</v>
-      </c>
-      <c r="S76" s="3">
-        <v>3700</v>
       </c>
       <c r="T76" s="3">
         <v>3700</v>
       </c>
       <c r="U76" s="3">
-        <v>3800</v>
+        <v>3700</v>
       </c>
       <c r="V76" s="3">
         <v>3800</v>
       </c>
       <c r="W76" s="3">
+        <v>3800</v>
+      </c>
+      <c r="X76" s="3">
         <v>3600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6392,170 +6581,176 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45108</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45017</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44835</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44744</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44653</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44562</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44471</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44380</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44289</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44198</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44100</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44009</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43918</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43827</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43736</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43645</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43554</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43463</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43372</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43099</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42917</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42826</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-300</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-200</v>
       </c>
       <c r="H81" s="3">
         <v>-200</v>
       </c>
       <c r="I81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J81" s="3">
         <v>200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-100</v>
       </c>
-      <c r="K81" s="3">
-        <v>100</v>
-      </c>
       <c r="L81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N81" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O81" s="3">
         <v>200</v>
       </c>
       <c r="P81" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q81" s="3">
         <v>100</v>
       </c>
       <c r="R81" s="3">
+        <v>100</v>
+      </c>
+      <c r="S81" s="3">
         <v>200</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3">
         <v>-100</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
       <c r="V81" s="3">
+        <v>0</v>
+      </c>
+      <c r="W81" s="3">
         <v>200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-100</v>
       </c>
-      <c r="X81" s="3">
-        <v>100</v>
-      </c>
       <c r="Y81" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Z81" s="3">
         <v>300</v>
@@ -6567,16 +6762,19 @@
         <v>300</v>
       </c>
       <c r="AC81" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD81" s="3">
         <v>-200</v>
       </c>
-      <c r="AD81" s="3">
-        <v>100</v>
-      </c>
       <c r="AE81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6608,8 +6806,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6697,8 +6896,11 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6786,8 +6988,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6875,8 +7080,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6964,8 +7172,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7053,8 +7264,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7142,65 +7356,68 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>100</v>
+      </c>
+      <c r="E89" s="3">
         <v>200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-700</v>
       </c>
-      <c r="F89" s="3">
-        <v>100</v>
-      </c>
       <c r="G89" s="3">
+        <v>100</v>
+      </c>
+      <c r="H89" s="3">
         <v>-200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1000</v>
       </c>
-      <c r="N89" s="3">
-        <v>100</v>
-      </c>
       <c r="O89" s="3">
+        <v>100</v>
+      </c>
+      <c r="P89" s="3">
         <v>300</v>
       </c>
-      <c r="P89" s="3">
-        <v>100</v>
-      </c>
       <c r="Q89" s="3">
+        <v>100</v>
+      </c>
+      <c r="R89" s="3">
         <v>400</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
       <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
         <v>-400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>300</v>
       </c>
-      <c r="U89" s="3">
-        <v>100</v>
-      </c>
       <c r="V89" s="3">
         <v>100</v>
       </c>
@@ -7208,31 +7425,34 @@
         <v>100</v>
       </c>
       <c r="X89" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>200</v>
       </c>
-      <c r="AB89" s="3">
-        <v>100</v>
-      </c>
       <c r="AC89" s="3">
         <v>100</v>
       </c>
       <c r="AD89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE89" s="3">
         <v>-100</v>
       </c>
-      <c r="AE89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7264,8 +7484,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7353,8 +7574,11 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7442,8 +7666,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7531,8 +7758,11 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7593,8 +7823,8 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>24</v>
+      <c r="W94" s="3">
+        <v>0</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>24</v>
@@ -7602,8 +7832,8 @@
       <c r="Y94" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
+      <c r="Z94" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
@@ -7620,8 +7850,11 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7653,8 +7886,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7742,8 +7976,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7831,8 +8068,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7920,8 +8160,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8009,8 +8252,11 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8020,8 +8266,8 @@
       <c r="E100" s="3">
         <v>0</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>24</v>
+      <c r="F100" s="3">
+        <v>0</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>24</v>
@@ -8032,11 +8278,11 @@
       <c r="I100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K100" s="3">
         <v>-500</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>24</v>
@@ -8044,18 +8290,18 @@
       <c r="M100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
+      <c r="N100" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
-      <c r="P100" s="3" t="s">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
@@ -8098,8 +8344,11 @@
       <c r="AE100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8187,93 +8436,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>100</v>
+      </c>
+      <c r="E102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-700</v>
       </c>
-      <c r="F102" s="3">
-        <v>100</v>
-      </c>
       <c r="G102" s="3">
+        <v>100</v>
+      </c>
+      <c r="H102" s="3">
         <v>-200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1000</v>
       </c>
-      <c r="N102" s="3">
-        <v>100</v>
-      </c>
       <c r="O102" s="3">
+        <v>100</v>
+      </c>
+      <c r="P102" s="3">
         <v>300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>400</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>-400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>300</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
       <c r="V102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W102" s="3">
+        <v>100</v>
+      </c>
+      <c r="X102" s="3">
         <v>-100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>200</v>
       </c>
-      <c r="AB102" s="3">
-        <v>100</v>
-      </c>
       <c r="AC102" s="3">
         <v>100</v>
       </c>
       <c r="AD102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE102" s="3">
         <v>-100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TOFB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TOFB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
   <si>
     <t>TOFB</t>
   </si>
@@ -656,222 +656,229 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45290</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45108</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45017</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44835</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44744</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44653</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44562</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44471</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44380</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44289</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44198</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44100</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44009</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43918</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43827</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43736</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43645</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43554</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43463</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43372</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43099</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42917</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42826</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2500</v>
+        <v>2200</v>
       </c>
       <c r="E8" s="3">
-        <v>2700</v>
+        <v>2300</v>
       </c>
       <c r="F8" s="3">
         <v>2500</v>
       </c>
       <c r="G8" s="3">
+        <v>2700</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I8" s="3">
         <v>3500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>2900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>3000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>3500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>3100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>3400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>3000</v>
-      </c>
-      <c r="N8" s="3">
-        <v>3200</v>
-      </c>
-      <c r="O8" s="3">
-        <v>4200</v>
       </c>
       <c r="P8" s="3">
         <v>3200</v>
       </c>
       <c r="Q8" s="3">
-        <v>3200</v>
+        <v>4200</v>
       </c>
       <c r="R8" s="3">
         <v>3200</v>
       </c>
       <c r="S8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="T8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="U8" s="3">
         <v>3400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>3100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>3100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>3500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>3000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>2800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>3400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>3800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>3900</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>3300</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>3600</v>
       </c>
       <c r="AD8" s="3">
         <v>3300</v>
@@ -880,10 +887,16 @@
         <v>3600</v>
       </c>
       <c r="AF8" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AG8" s="3">
         <v>3600</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -891,183 +904,195 @@
         <v>1700</v>
       </c>
       <c r="E9" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G9" s="3">
         <v>2100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>3000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>2500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>2500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>2600</v>
-      </c>
-      <c r="K9" s="3">
-        <v>2300</v>
-      </c>
-      <c r="L9" s="3">
-        <v>2500</v>
       </c>
       <c r="M9" s="3">
         <v>2300</v>
       </c>
       <c r="N9" s="3">
-        <v>2100</v>
+        <v>2500</v>
       </c>
       <c r="O9" s="3">
-        <v>3000</v>
+        <v>2300</v>
       </c>
       <c r="P9" s="3">
         <v>2100</v>
       </c>
       <c r="Q9" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R9" s="3">
+        <v>2100</v>
+      </c>
+      <c r="S9" s="3">
         <v>2200</v>
-      </c>
-      <c r="R9" s="3">
-        <v>2200</v>
-      </c>
-      <c r="S9" s="3">
-        <v>2100</v>
       </c>
       <c r="T9" s="3">
         <v>2200</v>
       </c>
       <c r="U9" s="3">
+        <v>2100</v>
+      </c>
+      <c r="V9" s="3">
+        <v>2200</v>
+      </c>
+      <c r="W9" s="3">
         <v>2300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>2500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>2000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>2000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>2400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>2500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>2600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>2100</v>
-      </c>
-      <c r="AC9" s="3">
-        <v>2500</v>
-      </c>
-      <c r="AD9" s="3">
-        <v>2300</v>
       </c>
       <c r="AE9" s="3">
         <v>2500</v>
       </c>
       <c r="AF9" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AG9" s="3">
         <v>2500</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>700</v>
+      </c>
+      <c r="F10" s="3">
         <v>800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>600</v>
-      </c>
-      <c r="G10" s="3">
-        <v>500</v>
-      </c>
-      <c r="H10" s="3">
-        <v>400</v>
       </c>
       <c r="I10" s="3">
         <v>500</v>
       </c>
       <c r="J10" s="3">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="K10" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="L10" s="3">
         <v>900</v>
       </c>
       <c r="M10" s="3">
+        <v>800</v>
+      </c>
+      <c r="N10" s="3">
+        <v>900</v>
+      </c>
+      <c r="O10" s="3">
         <v>700</v>
-      </c>
-      <c r="N10" s="3">
-        <v>1100</v>
-      </c>
-      <c r="O10" s="3">
-        <v>1200</v>
       </c>
       <c r="P10" s="3">
         <v>1100</v>
       </c>
       <c r="Q10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R10" s="3">
+        <v>1100</v>
+      </c>
+      <c r="S10" s="3">
         <v>1000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>1000</v>
-      </c>
-      <c r="W10" s="3">
-        <v>1000</v>
-      </c>
-      <c r="X10" s="3">
-        <v>800</v>
       </c>
       <c r="Y10" s="3">
         <v>1000</v>
       </c>
       <c r="Z10" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AB10" s="3">
         <v>1300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>1300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>1200</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>1100</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>1000</v>
       </c>
       <c r="AE10" s="3">
         <v>1100</v>
       </c>
       <c r="AF10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AG10" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1100,8 +1125,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1115,7 +1142,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12" s="3">
         <v>0</v>
@@ -1142,10 +1169,10 @@
         <v>0</v>
       </c>
       <c r="P12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R12" s="3">
         <v>100</v>
@@ -1192,8 +1219,14 @@
       <c r="AF12" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH12" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1284,13 +1317,19 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1308,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-200</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>24</v>
@@ -1325,11 +1364,11 @@
       <c r="O14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1376,8 +1415,14 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1468,8 +1513,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1499,58 +1550,60 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E17" s="3">
         <v>2400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="G17" s="3">
         <v>2900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>3900</v>
-      </c>
-      <c r="H17" s="3">
-        <v>3200</v>
-      </c>
-      <c r="I17" s="3">
-        <v>3300</v>
       </c>
       <c r="J17" s="3">
         <v>3200</v>
       </c>
       <c r="K17" s="3">
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="L17" s="3">
         <v>3200</v>
       </c>
       <c r="M17" s="3">
+        <v>3100</v>
+      </c>
+      <c r="N17" s="3">
+        <v>3200</v>
+      </c>
+      <c r="O17" s="3">
         <v>3000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>3000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>3800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>3000</v>
-      </c>
-      <c r="R17" s="3">
-        <v>3200</v>
-      </c>
-      <c r="S17" s="3">
-        <v>3200</v>
       </c>
       <c r="T17" s="3">
         <v>3200</v>
@@ -1559,69 +1612,75 @@
         <v>3200</v>
       </c>
       <c r="V17" s="3">
+        <v>3200</v>
+      </c>
+      <c r="W17" s="3">
+        <v>3200</v>
+      </c>
+      <c r="X17" s="3">
         <v>3500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>3000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>2900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>3300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>3400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>3500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>3000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>3400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>3400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>3500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="E18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="3">
+        <v>100</v>
+      </c>
+      <c r="G18" s="3">
         <v>-200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>300</v>
-      </c>
-      <c r="K18" s="3">
-        <v>0</v>
-      </c>
-      <c r="L18" s="3">
-        <v>200</v>
       </c>
       <c r="M18" s="3">
         <v>0</v>
@@ -1630,61 +1689,67 @@
         <v>200</v>
       </c>
       <c r="O18" s="3">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q18" s="3">
         <v>400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>300</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>200</v>
-      </c>
-      <c r="R18" s="3">
-        <v>0</v>
       </c>
       <c r="S18" s="3">
         <v>200</v>
       </c>
       <c r="T18" s="3">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3">
+        <v>200</v>
+      </c>
+      <c r="V18" s="3">
         <v>-100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-100</v>
       </c>
-      <c r="V18" s="3">
-        <v>0</v>
-      </c>
-      <c r="W18" s="3">
-        <v>0</v>
-      </c>
       <c r="X18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-100</v>
       </c>
-      <c r="Y18" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB18" s="3">
         <v>400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-100</v>
       </c>
-      <c r="AE18" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1717,8 +1782,10 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1753,14 +1820,14 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1809,82 +1876,88 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="3">
-        <v>100</v>
-      </c>
-      <c r="E21" s="3">
-        <v>-200</v>
+      <c r="D21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="F21" s="3">
+        <v>100</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L21" s="3">
+        <v>200</v>
+      </c>
+      <c r="M21" s="3">
         <v>-100</v>
       </c>
-      <c r="G21" s="3">
-        <v>-400</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J21" s="3">
-        <v>200</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L21" s="3">
-        <v>100</v>
-      </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
       <c r="N21" s="3">
         <v>100</v>
       </c>
       <c r="O21" s="3">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q21" s="3">
         <v>300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>300</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>200</v>
-      </c>
-      <c r="R21" s="3">
-        <v>100</v>
       </c>
       <c r="S21" s="3">
         <v>200</v>
       </c>
       <c r="T21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U21" s="3">
+        <v>200</v>
+      </c>
+      <c r="V21" s="3">
+        <v>0</v>
+      </c>
+      <c r="W21" s="3">
         <v>-100</v>
       </c>
-      <c r="V21" s="3">
-        <v>0</v>
-      </c>
-      <c r="W21" s="3">
-        <v>100</v>
-      </c>
       <c r="X21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-100</v>
       </c>
-      <c r="Y21" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>300</v>
-      </c>
       <c r="AA21" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AB21" s="3">
         <v>300</v>
@@ -1893,24 +1966,30 @@
         <v>300</v>
       </c>
       <c r="AD21" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE21" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF21" s="3">
         <v>-200</v>
       </c>
-      <c r="AE21" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF21" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
         <v>0</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="E22" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -1993,82 +2072,88 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="E23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F23" s="3">
+        <v>100</v>
+      </c>
+      <c r="G23" s="3">
         <v>-200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-100</v>
       </c>
-      <c r="L23" s="3">
-        <v>100</v>
-      </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
       <c r="N23" s="3">
         <v>100</v>
       </c>
       <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q23" s="3">
         <v>300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>200</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>200</v>
-      </c>
-      <c r="R23" s="3">
-        <v>100</v>
       </c>
       <c r="S23" s="3">
         <v>200</v>
       </c>
       <c r="T23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U23" s="3">
+        <v>200</v>
+      </c>
+      <c r="V23" s="3">
+        <v>0</v>
+      </c>
+      <c r="W23" s="3">
         <v>-100</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
       <c r="X23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="3">
         <v>-100</v>
       </c>
-      <c r="Y23" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>300</v>
-      </c>
       <c r="AA23" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AB23" s="3">
         <v>300</v>
@@ -2077,16 +2162,22 @@
         <v>300</v>
       </c>
       <c r="AD23" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE23" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF23" s="3">
         <v>-200</v>
       </c>
-      <c r="AE23" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -2094,25 +2185,25 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
       <c r="G24" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="H24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I24" s="3">
         <v>-100</v>
       </c>
       <c r="J24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -2124,19 +2215,19 @@
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>100</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
       <c r="S24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
@@ -2148,26 +2239,26 @@
         <v>0</v>
       </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>-200</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
       <c r="Z24" s="3">
         <v>0</v>
       </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>-100</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
       <c r="AD24" s="3">
         <v>0</v>
       </c>
@@ -2177,8 +2268,14 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2269,192 +2366,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="E26" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="F26" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="G26" s="3">
         <v>-300</v>
       </c>
       <c r="H26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J26" s="3">
         <v>-200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-100</v>
       </c>
-      <c r="L26" s="3">
-        <v>100</v>
-      </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
       <c r="N26" s="3">
         <v>100</v>
       </c>
       <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q26" s="3">
         <v>200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>200</v>
       </c>
-      <c r="Q26" s="3">
-        <v>100</v>
-      </c>
-      <c r="R26" s="3">
-        <v>100</v>
-      </c>
       <c r="S26" s="3">
+        <v>100</v>
+      </c>
+      <c r="T26" s="3">
+        <v>100</v>
+      </c>
+      <c r="U26" s="3">
         <v>200</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
+        <v>0</v>
+      </c>
+      <c r="W26" s="3">
         <v>-100</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
         <v>200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-100</v>
       </c>
-      <c r="Y26" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>300</v>
-      </c>
       <c r="AA26" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="AB26" s="3">
         <v>300</v>
       </c>
       <c r="AC26" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD26" s="3">
         <v>300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF26" s="3">
         <v>-200</v>
       </c>
-      <c r="AE26" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="E27" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="G27" s="3">
         <v>-300</v>
       </c>
       <c r="H27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J27" s="3">
         <v>-200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-100</v>
       </c>
-      <c r="L27" s="3">
-        <v>100</v>
-      </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
       <c r="N27" s="3">
         <v>100</v>
       </c>
       <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q27" s="3">
         <v>200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>200</v>
       </c>
-      <c r="Q27" s="3">
-        <v>100</v>
-      </c>
-      <c r="R27" s="3">
-        <v>100</v>
-      </c>
       <c r="S27" s="3">
+        <v>100</v>
+      </c>
+      <c r="T27" s="3">
+        <v>100</v>
+      </c>
+      <c r="U27" s="3">
         <v>200</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
+        <v>0</v>
+      </c>
+      <c r="W27" s="3">
         <v>-100</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
         <v>200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-100</v>
       </c>
-      <c r="Y27" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>300</v>
-      </c>
       <c r="AA27" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="AB27" s="3">
         <v>300</v>
       </c>
       <c r="AC27" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD27" s="3">
         <v>300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF27" s="3">
         <v>-200</v>
       </c>
-      <c r="AE27" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2545,8 +2660,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2601,11 +2722,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>24</v>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>24</v>
@@ -2619,14 +2740,14 @@
       <c r="Z29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA29" s="3">
-        <v>-200</v>
+      <c r="AA29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>24</v>
+      <c r="AC29" s="3">
+        <v>-200</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>24</v>
@@ -2637,8 +2758,14 @@
       <c r="AF29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2729,8 +2856,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2821,8 +2954,14 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2857,13 +2996,13 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
       <c r="P32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -2913,82 +3052,88 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="E33" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="F33" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="G33" s="3">
         <v>-300</v>
       </c>
       <c r="H33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J33" s="3">
         <v>-200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-100</v>
       </c>
-      <c r="L33" s="3">
-        <v>100</v>
-      </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
       <c r="N33" s="3">
         <v>100</v>
       </c>
       <c r="O33" s="3">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q33" s="3">
         <v>200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>200</v>
       </c>
-      <c r="Q33" s="3">
-        <v>100</v>
-      </c>
-      <c r="R33" s="3">
-        <v>100</v>
-      </c>
       <c r="S33" s="3">
+        <v>100</v>
+      </c>
+      <c r="T33" s="3">
+        <v>100</v>
+      </c>
+      <c r="U33" s="3">
         <v>200</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
+        <v>0</v>
+      </c>
+      <c r="W33" s="3">
         <v>-100</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
         <v>200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-100</v>
       </c>
-      <c r="Y33" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>300</v>
-      </c>
       <c r="AA33" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AB33" s="3">
         <v>300</v>
@@ -2997,16 +3142,22 @@
         <v>300</v>
       </c>
       <c r="AD33" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE33" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF33" s="3">
         <v>-200</v>
       </c>
-      <c r="AE33" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3097,82 +3248,88 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="E35" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="F35" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="G35" s="3">
         <v>-300</v>
       </c>
       <c r="H35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J35" s="3">
         <v>-200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-100</v>
       </c>
-      <c r="L35" s="3">
-        <v>100</v>
-      </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
       <c r="N35" s="3">
         <v>100</v>
       </c>
       <c r="O35" s="3">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q35" s="3">
         <v>200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>200</v>
       </c>
-      <c r="Q35" s="3">
-        <v>100</v>
-      </c>
-      <c r="R35" s="3">
-        <v>100</v>
-      </c>
       <c r="S35" s="3">
+        <v>100</v>
+      </c>
+      <c r="T35" s="3">
+        <v>100</v>
+      </c>
+      <c r="U35" s="3">
         <v>200</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3">
         <v>-100</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
         <v>200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-100</v>
       </c>
-      <c r="Y35" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>300</v>
-      </c>
       <c r="AA35" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AB35" s="3">
         <v>300</v>
@@ -3181,113 +3338,125 @@
         <v>300</v>
       </c>
       <c r="AD35" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE35" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF35" s="3">
         <v>-200</v>
       </c>
-      <c r="AE35" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45290</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45108</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45017</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44835</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44744</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44653</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44562</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44471</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44380</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44289</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44198</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44100</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44009</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43918</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43827</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43736</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43645</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43554</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43463</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43372</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43099</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42917</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42826</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3320,8 +3489,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3354,100 +3525,108 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>800</v>
+      </c>
+      <c r="F41" s="3">
         <v>700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>3000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>1400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>300</v>
-      </c>
-      <c r="AD41" s="3">
-        <v>200</v>
-      </c>
-      <c r="AE41" s="3">
-        <v>100</v>
       </c>
       <c r="AF41" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH41" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3538,100 +3717,112 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="E43" s="3">
         <v>800</v>
       </c>
       <c r="F43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G43" s="3">
+        <v>800</v>
+      </c>
+      <c r="H43" s="3">
         <v>900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1100</v>
-      </c>
-      <c r="J43" s="3">
-        <v>1400</v>
-      </c>
-      <c r="K43" s="3">
-        <v>1300</v>
       </c>
       <c r="L43" s="3">
         <v>1400</v>
       </c>
       <c r="M43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N43" s="3">
         <v>1400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P43" s="3">
         <v>1300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>2100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>2100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>2100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>1900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>2200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>2400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>1800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>2300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>2100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>1800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>2600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3639,34 +3830,34 @@
         <v>2500</v>
       </c>
       <c r="E44" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F44" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G44" s="3">
         <v>2400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>2600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>2500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>2700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>2600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>2400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1700</v>
-      </c>
-      <c r="M44" s="3">
-        <v>2000</v>
-      </c>
-      <c r="N44" s="3">
-        <v>2000</v>
       </c>
       <c r="O44" s="3">
         <v>2000</v>
@@ -3675,55 +3866,61 @@
         <v>2000</v>
       </c>
       <c r="Q44" s="3">
+        <v>2000</v>
+      </c>
+      <c r="R44" s="3">
+        <v>2000</v>
+      </c>
+      <c r="S44" s="3">
         <v>2100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>1900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>1900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>1800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>2100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>2300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>1700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>1900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>2000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>2000</v>
-      </c>
-      <c r="AA44" s="3">
-        <v>1500</v>
-      </c>
-      <c r="AB44" s="3">
-        <v>1700</v>
       </c>
       <c r="AC44" s="3">
         <v>1500</v>
       </c>
       <c r="AD44" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AE44" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AF44" s="3">
         <v>2000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>1600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3743,16 +3940,16 @@
         <v>100</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M45" s="3">
         <v>100</v>
@@ -3797,10 +3994,10 @@
         <v>100</v>
       </c>
       <c r="AA45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC45" s="3">
         <v>200</v>
@@ -3814,100 +4011,112 @@
       <c r="AF45" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH45" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F46" s="3">
         <v>4300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>4000</v>
-      </c>
-      <c r="G46" s="3">
-        <v>4900</v>
-      </c>
-      <c r="H46" s="3">
-        <v>4900</v>
       </c>
       <c r="I46" s="3">
         <v>4900</v>
       </c>
       <c r="J46" s="3">
+        <v>4900</v>
+      </c>
+      <c r="K46" s="3">
+        <v>4900</v>
+      </c>
+      <c r="L46" s="3">
         <v>5400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>5000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>6200</v>
-      </c>
-      <c r="M46" s="3">
-        <v>5600</v>
-      </c>
-      <c r="N46" s="3">
-        <v>5900</v>
       </c>
       <c r="O46" s="3">
         <v>5600</v>
       </c>
       <c r="P46" s="3">
+        <v>5900</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>5600</v>
+      </c>
+      <c r="R46" s="3">
         <v>5100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>4900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>4300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>4400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>4500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>4600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>4700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>4500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>4400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>4900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>5200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>4800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>4600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>4100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>4200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>4500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3998,8 +4207,14 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4007,70 +4222,70 @@
         <v>100</v>
       </c>
       <c r="E48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G48" s="3">
         <v>200</v>
       </c>
       <c r="H48" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I48" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L48" s="3">
         <v>200</v>
       </c>
       <c r="M48" s="3">
+        <v>200</v>
+      </c>
+      <c r="N48" s="3">
+        <v>200</v>
+      </c>
+      <c r="O48" s="3">
         <v>300</v>
-      </c>
-      <c r="N48" s="3">
-        <v>300</v>
-      </c>
-      <c r="O48" s="3">
-        <v>400</v>
       </c>
       <c r="P48" s="3">
         <v>300</v>
       </c>
       <c r="Q48" s="3">
+        <v>400</v>
+      </c>
+      <c r="R48" s="3">
         <v>300</v>
       </c>
-      <c r="R48" s="3">
-        <v>400</v>
-      </c>
       <c r="S48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="T48" s="3">
         <v>400</v>
       </c>
       <c r="U48" s="3">
+        <v>400</v>
+      </c>
+      <c r="V48" s="3">
+        <v>400</v>
+      </c>
+      <c r="W48" s="3">
         <v>200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>200</v>
       </c>
-      <c r="W48" s="3">
-        <v>100</v>
-      </c>
-      <c r="X48" s="3">
-        <v>100</v>
-      </c>
       <c r="Y48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA48" s="3">
         <v>0</v>
@@ -4090,8 +4305,14 @@
       <c r="AF48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4182,8 +4403,14 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4274,8 +4501,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4366,35 +4599,41 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>300</v>
+      </c>
+      <c r="F52" s="3">
         <v>200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>200</v>
       </c>
-      <c r="J52" s="3">
-        <v>100</v>
-      </c>
-      <c r="K52" s="3">
-        <v>100</v>
-      </c>
       <c r="L52" s="3">
         <v>100</v>
       </c>
@@ -4408,35 +4647,35 @@
         <v>100</v>
       </c>
       <c r="P52" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>100</v>
+      </c>
+      <c r="R52" s="3">
         <v>200</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>200</v>
-      </c>
-      <c r="R52" s="3">
-        <v>300</v>
       </c>
       <c r="S52" s="3">
         <v>200</v>
       </c>
       <c r="T52" s="3">
+        <v>300</v>
+      </c>
+      <c r="U52" s="3">
         <v>200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
+        <v>200</v>
+      </c>
+      <c r="W52" s="3">
         <v>500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>200</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>0</v>
-      </c>
       <c r="Z52" s="3">
         <v>0</v>
       </c>
@@ -4458,8 +4697,14 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4550,100 +4795,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F54" s="3">
         <v>4700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>4300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>4600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>5500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>5300</v>
-      </c>
-      <c r="I54" s="3">
-        <v>5300</v>
-      </c>
-      <c r="J54" s="3">
-        <v>5800</v>
       </c>
       <c r="K54" s="3">
         <v>5300</v>
       </c>
       <c r="L54" s="3">
+        <v>5800</v>
+      </c>
+      <c r="M54" s="3">
+        <v>5300</v>
+      </c>
+      <c r="N54" s="3">
         <v>6500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>6000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>6300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>6100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>5600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>5400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>4900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>5000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>5100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>5300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>5400</v>
-      </c>
-      <c r="W54" s="3">
-        <v>4900</v>
-      </c>
-      <c r="X54" s="3">
-        <v>4500</v>
       </c>
       <c r="Y54" s="3">
         <v>4900</v>
       </c>
       <c r="Z54" s="3">
-        <v>5300</v>
+        <v>4500</v>
       </c>
       <c r="AA54" s="3">
         <v>4900</v>
       </c>
       <c r="AB54" s="3">
+        <v>5300</v>
+      </c>
+      <c r="AC54" s="3">
+        <v>4900</v>
+      </c>
+      <c r="AD54" s="3">
         <v>4700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>4100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>4200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>4500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4676,8 +4933,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4710,100 +4969,108 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E57" s="3">
         <v>200</v>
       </c>
       <c r="F57" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G57" s="3">
+        <v>200</v>
+      </c>
+      <c r="H57" s="3">
+        <v>100</v>
+      </c>
+      <c r="I57" s="3">
         <v>700</v>
-      </c>
-      <c r="H57" s="3">
-        <v>400</v>
-      </c>
-      <c r="I57" s="3">
-        <v>200</v>
       </c>
       <c r="J57" s="3">
         <v>400</v>
       </c>
       <c r="K57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L57" s="3">
+        <v>400</v>
+      </c>
+      <c r="M57" s="3">
+        <v>100</v>
+      </c>
+      <c r="N57" s="3">
         <v>800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>300</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
-      </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3">
         <v>200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>300</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>500</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>700</v>
       </c>
       <c r="AA57" s="3">
         <v>500</v>
       </c>
       <c r="AB57" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="AC57" s="3">
         <v>500</v>
       </c>
       <c r="AD57" s="3">
+        <v>600</v>
+      </c>
+      <c r="AE57" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF57" s="3">
         <v>900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>1100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4829,22 +5096,22 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L58" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M58" s="3">
         <v>200</v>
       </c>
       <c r="N58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O58" s="3">
-        <v>100</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>24</v>
+        <v>200</v>
+      </c>
+      <c r="P58" s="3">
+        <v>100</v>
       </c>
       <c r="Q58" s="3">
         <v>100</v>
@@ -4852,8 +5119,8 @@
       <c r="R58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>24</v>
+      <c r="S58" s="3">
+        <v>100</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>24</v>
@@ -4864,11 +5131,11 @@
       <c r="V58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -4894,28 +5161,34 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>500</v>
+      </c>
+      <c r="F59" s="3">
         <v>300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>600</v>
-      </c>
-      <c r="H59" s="3">
-        <v>500</v>
-      </c>
-      <c r="I59" s="3">
-        <v>400</v>
       </c>
       <c r="J59" s="3">
         <v>500</v>
@@ -4924,34 +5197,34 @@
         <v>400</v>
       </c>
       <c r="L59" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="M59" s="3">
         <v>400</v>
       </c>
       <c r="N59" s="3">
+        <v>400</v>
+      </c>
+      <c r="O59" s="3">
+        <v>400</v>
+      </c>
+      <c r="P59" s="3">
         <v>500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>400</v>
-      </c>
-      <c r="T59" s="3">
-        <v>300</v>
-      </c>
-      <c r="U59" s="3">
-        <v>300</v>
       </c>
       <c r="V59" s="3">
         <v>300</v>
@@ -4960,54 +5233,60 @@
         <v>300</v>
       </c>
       <c r="X59" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Y59" s="3">
         <v>300</v>
       </c>
       <c r="Z59" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA59" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB59" s="3">
         <v>500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>600</v>
+      </c>
+      <c r="E60" s="3">
         <v>800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
+        <v>800</v>
+      </c>
+      <c r="G60" s="3">
         <v>500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1300</v>
-      </c>
-      <c r="H60" s="3">
-        <v>900</v>
-      </c>
-      <c r="I60" s="3">
-        <v>700</v>
       </c>
       <c r="J60" s="3">
         <v>900</v>
@@ -5016,70 +5295,76 @@
         <v>700</v>
       </c>
       <c r="L60" s="3">
+        <v>900</v>
+      </c>
+      <c r="M60" s="3">
+        <v>700</v>
+      </c>
+      <c r="N60" s="3">
         <v>1300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>800</v>
-      </c>
-      <c r="Z60" s="3">
-        <v>1200</v>
-      </c>
-      <c r="AA60" s="3">
-        <v>1100</v>
       </c>
       <c r="AB60" s="3">
         <v>1200</v>
       </c>
       <c r="AC60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AD60" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AE60" s="3">
         <v>1000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>1400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>1500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5108,28 +5393,28 @@
         <v>0</v>
       </c>
       <c r="L61" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="M61" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="N61" s="3">
         <v>500</v>
       </c>
       <c r="O61" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="P61" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="Q61" s="3">
         <v>600</v>
       </c>
       <c r="R61" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="S61" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="T61" s="3">
         <v>500</v>
@@ -5170,8 +5455,14 @@
       <c r="AF61" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>500</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5182,31 +5473,31 @@
         <v>0</v>
       </c>
       <c r="F62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M62" s="3">
         <v>100</v>
       </c>
       <c r="N62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O62" s="3">
         <v>100</v>
@@ -5221,10 +5512,10 @@
         <v>100</v>
       </c>
       <c r="S62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U62" s="3">
         <v>200</v>
@@ -5232,11 +5523,11 @@
       <c r="V62" s="3">
         <v>200</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>24</v>
+      <c r="W62" s="3">
+        <v>200</v>
+      </c>
+      <c r="X62" s="3">
+        <v>200</v>
       </c>
       <c r="Y62" s="3" t="s">
         <v>24</v>
@@ -5244,11 +5535,11 @@
       <c r="Z62" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>0</v>
+      <c r="AA62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB62" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AC62" s="3">
         <v>0</v>
@@ -5262,8 +5553,14 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5354,8 +5651,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5446,8 +5749,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5538,100 +5847,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>800</v>
+      </c>
+      <c r="F66" s="3">
         <v>900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>800</v>
-      </c>
-      <c r="L66" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M66" s="3">
-        <v>1500</v>
       </c>
       <c r="N66" s="3">
         <v>1800</v>
       </c>
       <c r="O66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q66" s="3">
         <v>1700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1300</v>
-      </c>
-      <c r="Z66" s="3">
-        <v>1700</v>
-      </c>
-      <c r="AA66" s="3">
-        <v>1600</v>
       </c>
       <c r="AB66" s="3">
         <v>1700</v>
       </c>
       <c r="AC66" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AD66" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AE66" s="3">
         <v>1500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>1900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>2100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5664,8 +5985,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5756,8 +6079,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5848,8 +6177,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5940,8 +6275,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6032,100 +6373,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="E72" s="3">
         <v>3400</v>
       </c>
       <c r="F72" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G72" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H72" s="3">
         <v>3700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>3800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>4100</v>
-      </c>
-      <c r="I72" s="3">
-        <v>4300</v>
-      </c>
-      <c r="J72" s="3">
-        <v>4500</v>
       </c>
       <c r="K72" s="3">
         <v>4300</v>
       </c>
       <c r="L72" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="M72" s="3">
         <v>4300</v>
       </c>
       <c r="N72" s="3">
+        <v>4400</v>
+      </c>
+      <c r="O72" s="3">
+        <v>4300</v>
+      </c>
+      <c r="P72" s="3">
         <v>4200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>4200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>4000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>3800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>3600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>3600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>3400</v>
-      </c>
-      <c r="U72" s="3">
-        <v>3500</v>
-      </c>
-      <c r="V72" s="3">
-        <v>3500</v>
       </c>
       <c r="W72" s="3">
         <v>3500</v>
       </c>
       <c r="X72" s="3">
-        <v>3300</v>
+        <v>3500</v>
       </c>
       <c r="Y72" s="3">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="Z72" s="3">
         <v>3300</v>
       </c>
       <c r="AA72" s="3">
+        <v>3400</v>
+      </c>
+      <c r="AB72" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AC72" s="3">
         <v>3000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>2700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>2400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>2100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>2300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6216,8 +6569,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6308,8 +6667,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6400,100 +6765,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E76" s="3">
         <v>3800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
+        <v>3800</v>
+      </c>
+      <c r="G76" s="3">
         <v>3700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>4000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>4100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>4400</v>
-      </c>
-      <c r="I76" s="3">
-        <v>4600</v>
-      </c>
-      <c r="J76" s="3">
-        <v>4800</v>
       </c>
       <c r="K76" s="3">
         <v>4600</v>
       </c>
       <c r="L76" s="3">
+        <v>4800</v>
+      </c>
+      <c r="M76" s="3">
+        <v>4600</v>
+      </c>
+      <c r="N76" s="3">
         <v>4700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>4500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>4500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>4400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>4200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>4000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>3900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>3800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>3700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>3700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>3800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>3800</v>
-      </c>
-      <c r="X76" s="3">
-        <v>3600</v>
-      </c>
-      <c r="Y76" s="3">
-        <v>3700</v>
       </c>
       <c r="Z76" s="3">
         <v>3600</v>
       </c>
       <c r="AA76" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AB76" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AC76" s="3">
         <v>3200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>3000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>2600</v>
-      </c>
-      <c r="AD76" s="3">
-        <v>2400</v>
-      </c>
-      <c r="AE76" s="3">
-        <v>2500</v>
       </c>
       <c r="AF76" s="3">
         <v>2400</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AH76" s="3">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6584,179 +6961,191 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45290</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45108</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45017</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44835</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44744</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44653</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44562</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44471</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44380</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44289</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44198</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44100</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44009</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43918</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43827</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43736</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43645</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43554</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43463</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43372</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43099</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42917</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42826</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="E81" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="F81" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="G81" s="3">
         <v>-300</v>
       </c>
       <c r="H81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J81" s="3">
         <v>-200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-100</v>
       </c>
-      <c r="L81" s="3">
-        <v>100</v>
-      </c>
-      <c r="M81" s="3">
-        <v>0</v>
-      </c>
       <c r="N81" s="3">
         <v>100</v>
       </c>
       <c r="O81" s="3">
+        <v>0</v>
+      </c>
+      <c r="P81" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q81" s="3">
         <v>200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>200</v>
       </c>
-      <c r="Q81" s="3">
-        <v>100</v>
-      </c>
-      <c r="R81" s="3">
-        <v>100</v>
-      </c>
       <c r="S81" s="3">
+        <v>100</v>
+      </c>
+      <c r="T81" s="3">
+        <v>100</v>
+      </c>
+      <c r="U81" s="3">
         <v>200</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
+        <v>0</v>
+      </c>
+      <c r="W81" s="3">
         <v>-100</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="3">
         <v>200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-100</v>
       </c>
-      <c r="Y81" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>300</v>
-      </c>
       <c r="AA81" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AB81" s="3">
         <v>300</v>
@@ -6765,16 +7154,22 @@
         <v>300</v>
       </c>
       <c r="AD81" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE81" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF81" s="3">
         <v>-200</v>
       </c>
-      <c r="AE81" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6807,8 +7202,10 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6899,8 +7296,14 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6991,8 +7394,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7083,8 +7492,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7175,8 +7590,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7267,8 +7688,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7359,100 +7786,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>100</v>
+        <v>-500</v>
       </c>
       <c r="E89" s="3">
+        <v>100</v>
+      </c>
+      <c r="F89" s="3">
+        <v>100</v>
+      </c>
+      <c r="G89" s="3">
         <v>200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-700</v>
       </c>
-      <c r="G89" s="3">
-        <v>100</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
+        <v>100</v>
+      </c>
+      <c r="J89" s="3">
         <v>-200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1000</v>
       </c>
-      <c r="O89" s="3">
-        <v>100</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
+        <v>100</v>
+      </c>
+      <c r="R89" s="3">
         <v>300</v>
       </c>
-      <c r="Q89" s="3">
-        <v>100</v>
-      </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
+        <v>100</v>
+      </c>
+      <c r="T89" s="3">
         <v>400</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
         <v>-400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>300</v>
       </c>
-      <c r="V89" s="3">
-        <v>100</v>
-      </c>
-      <c r="W89" s="3">
-        <v>100</v>
-      </c>
       <c r="X89" s="3">
         <v>100</v>
       </c>
       <c r="Y89" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>200</v>
       </c>
-      <c r="AC89" s="3">
-        <v>100</v>
-      </c>
-      <c r="AD89" s="3">
-        <v>100</v>
-      </c>
       <c r="AE89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG89" s="3">
         <v>-100</v>
       </c>
-      <c r="AF89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7485,8 +7924,10 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7577,8 +8018,14 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7669,8 +8116,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7761,8 +8214,14 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7826,20 +8285,20 @@
       <c r="W94" s="3">
         <v>0</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>24</v>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
+        <v>0</v>
       </c>
       <c r="Z94" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>0</v>
+      <c r="AA94" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB94" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AC94" s="3">
         <v>0</v>
@@ -7853,8 +8312,14 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7887,8 +8352,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7979,8 +8446,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8071,8 +8544,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8163,8 +8642,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8255,8 +8740,14 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8269,11 +8760,11 @@
       <c r="F100" s="3">
         <v>0</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>24</v>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>24</v>
@@ -8281,32 +8772,32 @@
       <c r="J100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K100" s="3">
-        <v>-500</v>
+      <c r="K100" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>24</v>
+      <c r="M100" s="3">
+        <v>-500</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3" t="s">
+      <c r="O100" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="P100" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
+      <c r="S100" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="T100" s="3">
         <v>0</v>
@@ -8347,8 +8838,14 @@
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8439,96 +8936,108 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>100</v>
+        <v>-500</v>
       </c>
       <c r="E102" s="3">
+        <v>100</v>
+      </c>
+      <c r="F102" s="3">
+        <v>100</v>
+      </c>
+      <c r="G102" s="3">
         <v>200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-700</v>
       </c>
-      <c r="G102" s="3">
-        <v>100</v>
-      </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
+        <v>100</v>
+      </c>
+      <c r="J102" s="3">
         <v>-200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>1000</v>
       </c>
-      <c r="O102" s="3">
-        <v>100</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
+        <v>100</v>
+      </c>
+      <c r="R102" s="3">
         <v>300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>400</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>-400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>300</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
-      <c r="W102" s="3">
-        <v>100</v>
-      </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>200</v>
       </c>
-      <c r="AC102" s="3">
-        <v>100</v>
-      </c>
-      <c r="AD102" s="3">
-        <v>100</v>
-      </c>
       <c r="AE102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG102" s="3">
         <v>-100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TOFB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TOFB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>TOFB</t>
   </si>
@@ -656,196 +656,200 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E7" s="2">
         <v>45381</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45290</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45108</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45017</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44835</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44744</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44653</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44562</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44471</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44380</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44289</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44198</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44100</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44009</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43918</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43827</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43736</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43645</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43554</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43463</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43372</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43099</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42917</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42826</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E8" s="3">
         <v>2200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4200</v>
-      </c>
-      <c r="R8" s="3">
-        <v>3200</v>
       </c>
       <c r="S8" s="3">
         <v>3200</v>
@@ -854,245 +858,254 @@
         <v>3200</v>
       </c>
       <c r="U8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="V8" s="3">
         <v>3400</v>
-      </c>
-      <c r="V8" s="3">
-        <v>3100</v>
       </c>
       <c r="W8" s="3">
         <v>3100</v>
       </c>
       <c r="X8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Y8" s="3">
         <v>3500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3300</v>
-      </c>
-      <c r="AG8" s="3">
-        <v>3600</v>
       </c>
       <c r="AH8" s="3">
         <v>3600</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E9" s="3">
         <v>1700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3000</v>
-      </c>
-      <c r="J9" s="3">
-        <v>2500</v>
       </c>
       <c r="K9" s="3">
         <v>2500</v>
       </c>
       <c r="L9" s="3">
+        <v>2500</v>
+      </c>
+      <c r="M9" s="3">
         <v>2600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2100</v>
-      </c>
-      <c r="S9" s="3">
-        <v>2200</v>
       </c>
       <c r="T9" s="3">
         <v>2200</v>
       </c>
       <c r="U9" s="3">
+        <v>2200</v>
+      </c>
+      <c r="V9" s="3">
         <v>2100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2500</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>2000</v>
       </c>
       <c r="Z9" s="3">
         <v>2000</v>
       </c>
       <c r="AA9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AB9" s="3">
         <v>2400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2300</v>
-      </c>
-      <c r="AG9" s="3">
-        <v>2500</v>
       </c>
       <c r="AH9" s="3">
         <v>2500</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>700</v>
+      </c>
+      <c r="E10" s="3">
         <v>500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>800</v>
-      </c>
-      <c r="G10" s="3">
-        <v>600</v>
       </c>
       <c r="H10" s="3">
         <v>600</v>
       </c>
       <c r="I10" s="3">
+        <v>600</v>
+      </c>
+      <c r="J10" s="3">
         <v>500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1100</v>
-      </c>
-      <c r="S10" s="3">
-        <v>1000</v>
       </c>
       <c r="T10" s="3">
         <v>1000</v>
       </c>
       <c r="U10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V10" s="3">
         <v>1300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>800</v>
-      </c>
-      <c r="X10" s="3">
-        <v>1000</v>
       </c>
       <c r="Y10" s="3">
         <v>1000</v>
       </c>
       <c r="Z10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AA10" s="3">
         <v>800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1000</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>1300</v>
       </c>
       <c r="AC10" s="3">
         <v>1300</v>
       </c>
       <c r="AD10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AE10" s="3">
         <v>1200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1000</v>
-      </c>
-      <c r="AG10" s="3">
-        <v>1100</v>
       </c>
       <c r="AH10" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1127,8 +1140,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1136,16 +1150,16 @@
         <v>0</v>
       </c>
       <c r="E12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I12" s="3">
         <v>0</v>
@@ -1175,7 +1189,7 @@
         <v>0</v>
       </c>
       <c r="R12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S12" s="3">
         <v>100</v>
@@ -1225,8 +1239,11 @@
       <c r="AH12" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1323,16 +1340,19 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -1353,10 +1373,10 @@
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-200</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>24</v>
@@ -1370,8 +1390,8 @@
       <c r="Q14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1421,8 +1441,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1519,8 +1542,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1552,61 +1578,62 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E17" s="3">
         <v>2500</v>
-      </c>
-      <c r="E17" s="3">
-        <v>2400</v>
       </c>
       <c r="F17" s="3">
         <v>2400</v>
       </c>
       <c r="G17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H17" s="3">
         <v>2900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3200</v>
-      </c>
-      <c r="O17" s="3">
-        <v>3000</v>
       </c>
       <c r="P17" s="3">
         <v>3000</v>
       </c>
       <c r="Q17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R17" s="3">
         <v>3800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3000</v>
-      </c>
-      <c r="T17" s="3">
-        <v>3200</v>
       </c>
       <c r="U17" s="3">
         <v>3200</v>
@@ -1618,138 +1645,144 @@
         <v>3200</v>
       </c>
       <c r="X17" s="3">
+        <v>3200</v>
+      </c>
+      <c r="Y17" s="3">
         <v>3500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3000</v>
-      </c>
-      <c r="AE17" s="3">
-        <v>3400</v>
       </c>
       <c r="AF17" s="3">
         <v>3400</v>
       </c>
       <c r="AG17" s="3">
+        <v>3400</v>
+      </c>
+      <c r="AH17" s="3">
         <v>3500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
         <v>-300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-100</v>
       </c>
-      <c r="F18" s="3">
-        <v>100</v>
-      </c>
       <c r="G18" s="3">
+        <v>100</v>
+      </c>
+      <c r="H18" s="3">
         <v>-200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-400</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-300</v>
       </c>
       <c r="K18" s="3">
         <v>-300</v>
       </c>
       <c r="L18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M18" s="3">
         <v>300</v>
       </c>
-      <c r="M18" s="3">
-        <v>0</v>
-      </c>
       <c r="N18" s="3">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3">
         <v>200</v>
       </c>
-      <c r="O18" s="3">
-        <v>0</v>
-      </c>
       <c r="P18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3">
         <v>200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>200</v>
       </c>
-      <c r="T18" s="3">
-        <v>0</v>
-      </c>
       <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
         <v>200</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-100</v>
       </c>
       <c r="W18" s="3">
         <v>-100</v>
       </c>
       <c r="X18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y18" s="3">
         <v>0</v>
       </c>
       <c r="Z18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-100</v>
       </c>
-      <c r="AA18" s="3">
-        <v>100</v>
-      </c>
       <c r="AB18" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="AC18" s="3">
         <v>400</v>
       </c>
       <c r="AD18" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE18" s="3">
         <v>300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-100</v>
       </c>
-      <c r="AG18" s="3">
-        <v>100</v>
-      </c>
       <c r="AH18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1784,8 +1817,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1826,11 +1860,11 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1882,8 +1916,11 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1893,74 +1930,74 @@
       <c r="E21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F21" s="3">
-        <v>100</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="F21" s="3" t="s">
         <v>24</v>
+      </c>
+      <c r="G21" s="3">
+        <v>100</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="3">
         <v>-400</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-300</v>
       </c>
       <c r="K21" s="3">
         <v>-300</v>
       </c>
       <c r="L21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M21" s="3">
         <v>200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-100</v>
       </c>
-      <c r="N21" s="3">
-        <v>100</v>
-      </c>
       <c r="O21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="R21" s="3">
         <v>300</v>
       </c>
       <c r="S21" s="3">
+        <v>300</v>
+      </c>
+      <c r="T21" s="3">
         <v>200</v>
       </c>
-      <c r="T21" s="3">
-        <v>100</v>
-      </c>
       <c r="U21" s="3">
+        <v>100</v>
+      </c>
+      <c r="V21" s="3">
         <v>200</v>
       </c>
-      <c r="V21" s="3">
-        <v>0</v>
-      </c>
       <c r="W21" s="3">
+        <v>0</v>
+      </c>
+      <c r="X21" s="3">
         <v>-100</v>
       </c>
-      <c r="X21" s="3">
-        <v>0</v>
-      </c>
       <c r="Y21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-100</v>
       </c>
-      <c r="AA21" s="3">
-        <v>100</v>
-      </c>
       <c r="AB21" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AC21" s="3">
         <v>300</v>
@@ -1972,28 +2009,31 @@
         <v>300</v>
       </c>
       <c r="AF21" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG21" s="3">
         <v>-200</v>
       </c>
-      <c r="AG21" s="3">
-        <v>100</v>
-      </c>
       <c r="AH21" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
       <c r="G22" s="3">
         <v>0</v>
       </c>
@@ -2078,85 +2118,88 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
         <v>-300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-100</v>
       </c>
-      <c r="F23" s="3">
-        <v>100</v>
-      </c>
       <c r="G23" s="3">
+        <v>100</v>
+      </c>
+      <c r="H23" s="3">
         <v>-200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-400</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-300</v>
       </c>
       <c r="K23" s="3">
         <v>-300</v>
       </c>
       <c r="L23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M23" s="3">
         <v>200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-100</v>
       </c>
-      <c r="N23" s="3">
-        <v>100</v>
-      </c>
       <c r="O23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="3">
+        <v>100</v>
+      </c>
+      <c r="R23" s="3">
         <v>300</v>
-      </c>
-      <c r="R23" s="3">
-        <v>200</v>
       </c>
       <c r="S23" s="3">
         <v>200</v>
       </c>
       <c r="T23" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U23" s="3">
+        <v>100</v>
+      </c>
+      <c r="V23" s="3">
         <v>200</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
       <c r="W23" s="3">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3">
         <v>-100</v>
       </c>
-      <c r="X23" s="3">
-        <v>0</v>
-      </c>
       <c r="Y23" s="3">
         <v>0</v>
       </c>
       <c r="Z23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-100</v>
       </c>
-      <c r="AA23" s="3">
-        <v>100</v>
-      </c>
       <c r="AB23" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AC23" s="3">
         <v>300</v>
@@ -2168,16 +2211,19 @@
         <v>300</v>
       </c>
       <c r="AF23" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG23" s="3">
         <v>-200</v>
       </c>
-      <c r="AG23" s="3">
-        <v>100</v>
-      </c>
       <c r="AH23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -2191,13 +2237,13 @@
         <v>0</v>
       </c>
       <c r="G24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3">
         <v>-100</v>
@@ -2206,7 +2252,7 @@
         <v>-100</v>
       </c>
       <c r="L24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -2221,16 +2267,16 @@
         <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -2245,11 +2291,11 @@
         <v>0</v>
       </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-200</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
         <v>0</v>
       </c>
@@ -2257,11 +2303,11 @@
         <v>0</v>
       </c>
       <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
         <v>-100</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
       <c r="AE24" s="3">
         <v>0</v>
       </c>
@@ -2274,8 +2320,11 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2372,204 +2421,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
         <v>-300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-100</v>
       </c>
-      <c r="F26" s="3">
-        <v>100</v>
-      </c>
       <c r="G26" s="3">
+        <v>100</v>
+      </c>
+      <c r="H26" s="3">
         <v>-300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-300</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-200</v>
       </c>
       <c r="K26" s="3">
         <v>-200</v>
       </c>
       <c r="L26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M26" s="3">
         <v>200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-100</v>
       </c>
-      <c r="N26" s="3">
-        <v>100</v>
-      </c>
       <c r="O26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R26" s="3">
         <v>200</v>
       </c>
       <c r="S26" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T26" s="3">
         <v>100</v>
       </c>
       <c r="U26" s="3">
+        <v>100</v>
+      </c>
+      <c r="V26" s="3">
         <v>200</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
       <c r="W26" s="3">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3">
         <v>-100</v>
       </c>
-      <c r="X26" s="3">
-        <v>0</v>
-      </c>
       <c r="Y26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="3">
         <v>200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-100</v>
       </c>
-      <c r="AA26" s="3">
-        <v>100</v>
-      </c>
       <c r="AB26" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC26" s="3">
         <v>300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>400</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>300</v>
       </c>
       <c r="AE26" s="3">
         <v>300</v>
       </c>
       <c r="AF26" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG26" s="3">
         <v>-200</v>
       </c>
-      <c r="AG26" s="3">
-        <v>100</v>
-      </c>
       <c r="AH26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
         <v>-300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-100</v>
       </c>
-      <c r="F27" s="3">
-        <v>100</v>
-      </c>
       <c r="G27" s="3">
+        <v>100</v>
+      </c>
+      <c r="H27" s="3">
         <v>-300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-300</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-200</v>
       </c>
       <c r="K27" s="3">
         <v>-200</v>
       </c>
       <c r="L27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M27" s="3">
         <v>200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-100</v>
       </c>
-      <c r="N27" s="3">
-        <v>100</v>
-      </c>
       <c r="O27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R27" s="3">
         <v>200</v>
       </c>
       <c r="S27" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T27" s="3">
         <v>100</v>
       </c>
       <c r="U27" s="3">
+        <v>100</v>
+      </c>
+      <c r="V27" s="3">
         <v>200</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
       <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
         <v>-100</v>
       </c>
-      <c r="X27" s="3">
-        <v>0</v>
-      </c>
       <c r="Y27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="3">
         <v>200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-100</v>
       </c>
-      <c r="AA27" s="3">
-        <v>100</v>
-      </c>
       <c r="AB27" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC27" s="3">
         <v>300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>400</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>300</v>
       </c>
       <c r="AE27" s="3">
         <v>300</v>
       </c>
       <c r="AF27" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG27" s="3">
         <v>-200</v>
       </c>
-      <c r="AG27" s="3">
-        <v>100</v>
-      </c>
       <c r="AH27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2666,8 +2724,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2728,8 +2789,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>24</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>24</v>
@@ -2746,11 +2807,11 @@
       <c r="AB29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-200</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>24</v>
@@ -2764,8 +2825,11 @@
       <c r="AH29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2862,8 +2926,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2960,8 +3027,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3002,10 +3072,10 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -3058,85 +3128,88 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3">
         <v>-300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-100</v>
       </c>
-      <c r="F33" s="3">
-        <v>100</v>
-      </c>
       <c r="G33" s="3">
+        <v>100</v>
+      </c>
+      <c r="H33" s="3">
         <v>-300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-300</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-200</v>
       </c>
       <c r="K33" s="3">
         <v>-200</v>
       </c>
       <c r="L33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M33" s="3">
         <v>200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-100</v>
       </c>
-      <c r="N33" s="3">
-        <v>100</v>
-      </c>
       <c r="O33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R33" s="3">
         <v>200</v>
       </c>
       <c r="S33" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T33" s="3">
         <v>100</v>
       </c>
       <c r="U33" s="3">
+        <v>100</v>
+      </c>
+      <c r="V33" s="3">
         <v>200</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
       <c r="W33" s="3">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3">
         <v>-100</v>
       </c>
-      <c r="X33" s="3">
-        <v>0</v>
-      </c>
       <c r="Y33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="3">
         <v>200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-100</v>
       </c>
-      <c r="AA33" s="3">
-        <v>100</v>
-      </c>
       <c r="AB33" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AC33" s="3">
         <v>300</v>
@@ -3148,16 +3221,19 @@
         <v>300</v>
       </c>
       <c r="AF33" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG33" s="3">
         <v>-200</v>
       </c>
-      <c r="AG33" s="3">
-        <v>100</v>
-      </c>
       <c r="AH33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3254,85 +3330,88 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
         <v>-300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-100</v>
       </c>
-      <c r="F35" s="3">
-        <v>100</v>
-      </c>
       <c r="G35" s="3">
+        <v>100</v>
+      </c>
+      <c r="H35" s="3">
         <v>-300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-300</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-200</v>
       </c>
       <c r="K35" s="3">
         <v>-200</v>
       </c>
       <c r="L35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M35" s="3">
         <v>200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-100</v>
       </c>
-      <c r="N35" s="3">
-        <v>100</v>
-      </c>
       <c r="O35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R35" s="3">
         <v>200</v>
       </c>
       <c r="S35" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T35" s="3">
         <v>100</v>
       </c>
       <c r="U35" s="3">
+        <v>100</v>
+      </c>
+      <c r="V35" s="3">
         <v>200</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
       <c r="W35" s="3">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3">
         <v>-100</v>
       </c>
-      <c r="X35" s="3">
-        <v>0</v>
-      </c>
       <c r="Y35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="3">
         <v>200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-100</v>
       </c>
-      <c r="AA35" s="3">
-        <v>100</v>
-      </c>
       <c r="AB35" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AC35" s="3">
         <v>300</v>
@@ -3344,119 +3423,125 @@
         <v>300</v>
       </c>
       <c r="AF35" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG35" s="3">
         <v>-200</v>
       </c>
-      <c r="AG35" s="3">
-        <v>100</v>
-      </c>
       <c r="AH35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E38" s="2">
         <v>45381</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45290</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45108</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45017</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44835</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44744</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44653</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44562</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44471</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44380</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44289</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44198</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44100</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44009</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43918</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43827</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43736</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43645</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43554</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43463</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43372</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43099</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42917</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42826</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3491,8 +3576,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3527,106 +3613,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>500</v>
+      </c>
+      <c r="E41" s="3">
         <v>400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>900</v>
-      </c>
-      <c r="U41" s="3">
-        <v>500</v>
       </c>
       <c r="V41" s="3">
         <v>500</v>
       </c>
       <c r="W41" s="3">
+        <v>500</v>
+      </c>
+      <c r="X41" s="3">
         <v>900</v>
-      </c>
-      <c r="X41" s="3">
-        <v>600</v>
       </c>
       <c r="Y41" s="3">
         <v>600</v>
       </c>
       <c r="Z41" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AA41" s="3">
         <v>500</v>
       </c>
       <c r="AB41" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC41" s="3">
         <v>800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>200</v>
       </c>
-      <c r="AG41" s="3">
-        <v>100</v>
-      </c>
       <c r="AH41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI41" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3723,111 +3813,117 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>800</v>
+      </c>
+      <c r="E43" s="3">
         <v>900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1300</v>
-      </c>
-      <c r="N43" s="3">
-        <v>1400</v>
       </c>
       <c r="O43" s="3">
         <v>1400</v>
       </c>
       <c r="P43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Q43" s="3">
         <v>1300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2100</v>
-      </c>
-      <c r="R43" s="3">
-        <v>1600</v>
       </c>
       <c r="S43" s="3">
         <v>1600</v>
       </c>
       <c r="T43" s="3">
+        <v>1600</v>
+      </c>
+      <c r="U43" s="3">
         <v>1300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2500</v>
+        <v>2200</v>
       </c>
       <c r="E44" s="3">
         <v>2500</v>
@@ -3836,31 +3932,31 @@
         <v>2500</v>
       </c>
       <c r="G44" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H44" s="3">
         <v>2400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1700</v>
-      </c>
-      <c r="O44" s="3">
-        <v>2000</v>
       </c>
       <c r="P44" s="3">
         <v>2000</v>
@@ -3872,55 +3968,58 @@
         <v>2000</v>
       </c>
       <c r="S44" s="3">
+        <v>2000</v>
+      </c>
+      <c r="T44" s="3">
         <v>2100</v>
-      </c>
-      <c r="T44" s="3">
-        <v>1900</v>
       </c>
       <c r="U44" s="3">
         <v>1900</v>
       </c>
       <c r="V44" s="3">
+        <v>1900</v>
+      </c>
+      <c r="W44" s="3">
         <v>1800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1900</v>
-      </c>
-      <c r="AA44" s="3">
-        <v>2000</v>
       </c>
       <c r="AB44" s="3">
         <v>2000</v>
       </c>
       <c r="AC44" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AD44" s="3">
         <v>1500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2000</v>
-      </c>
-      <c r="AG44" s="3">
-        <v>1600</v>
       </c>
       <c r="AH44" s="3">
         <v>1600</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3946,13 +4045,13 @@
         <v>100</v>
       </c>
       <c r="K45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
       <c r="M45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N45" s="3">
         <v>100</v>
@@ -4000,7 +4099,7 @@
         <v>100</v>
       </c>
       <c r="AC45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AD45" s="3">
         <v>200</v>
@@ -4017,28 +4116,31 @@
       <c r="AH45" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E46" s="3">
         <v>3800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4000</v>
-      </c>
-      <c r="I46" s="3">
-        <v>4900</v>
       </c>
       <c r="J46" s="3">
         <v>4900</v>
@@ -4047,76 +4149,79 @@
         <v>4900</v>
       </c>
       <c r="L46" s="3">
+        <v>4900</v>
+      </c>
+      <c r="M46" s="3">
         <v>5400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4200</v>
-      </c>
-      <c r="AG46" s="3">
-        <v>4500</v>
       </c>
       <c r="AH46" s="3">
         <v>4500</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4213,8 +4318,11 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4228,7 +4336,7 @@
         <v>100</v>
       </c>
       <c r="G48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H48" s="3">
         <v>200</v>
@@ -4237,13 +4345,13 @@
         <v>200</v>
       </c>
       <c r="J48" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K48" s="3">
         <v>100</v>
       </c>
       <c r="L48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M48" s="3">
         <v>200</v>
@@ -4252,22 +4360,22 @@
         <v>200</v>
       </c>
       <c r="O48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P48" s="3">
         <v>300</v>
       </c>
       <c r="Q48" s="3">
+        <v>300</v>
+      </c>
+      <c r="R48" s="3">
         <v>400</v>
-      </c>
-      <c r="R48" s="3">
-        <v>300</v>
       </c>
       <c r="S48" s="3">
         <v>300</v>
       </c>
       <c r="T48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="U48" s="3">
         <v>400</v>
@@ -4276,19 +4384,19 @@
         <v>400</v>
       </c>
       <c r="W48" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="X48" s="3">
         <v>200</v>
       </c>
       <c r="Y48" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z48" s="3">
         <v>100</v>
       </c>
       <c r="AA48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB48" s="3">
         <v>0</v>
@@ -4311,8 +4419,11 @@
       <c r="AH48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4409,8 +4520,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4507,8 +4621,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4605,8 +4722,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4617,26 +4737,26 @@
         <v>300</v>
       </c>
       <c r="F52" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G52" s="3">
         <v>200</v>
       </c>
       <c r="H52" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="I52" s="3">
         <v>400</v>
       </c>
       <c r="J52" s="3">
+        <v>400</v>
+      </c>
+      <c r="K52" s="3">
         <v>300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>200</v>
       </c>
-      <c r="L52" s="3">
-        <v>100</v>
-      </c>
       <c r="M52" s="3">
         <v>100</v>
       </c>
@@ -4653,32 +4773,32 @@
         <v>100</v>
       </c>
       <c r="R52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S52" s="3">
         <v>200</v>
       </c>
       <c r="T52" s="3">
+        <v>200</v>
+      </c>
+      <c r="U52" s="3">
         <v>300</v>
-      </c>
-      <c r="U52" s="3">
-        <v>200</v>
       </c>
       <c r="V52" s="3">
         <v>200</v>
       </c>
       <c r="W52" s="3">
+        <v>200</v>
+      </c>
+      <c r="X52" s="3">
         <v>500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>200</v>
       </c>
-      <c r="Z52" s="3">
-        <v>0</v>
-      </c>
       <c r="AA52" s="3">
         <v>0</v>
       </c>
@@ -4703,8 +4823,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4801,106 +4924,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E54" s="3">
         <v>4200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5500</v>
-      </c>
-      <c r="J54" s="3">
-        <v>5300</v>
       </c>
       <c r="K54" s="3">
         <v>5300</v>
       </c>
       <c r="L54" s="3">
+        <v>5300</v>
+      </c>
+      <c r="M54" s="3">
         <v>5800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>4900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>4700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>4100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>4200</v>
-      </c>
-      <c r="AG54" s="3">
-        <v>4500</v>
       </c>
       <c r="AH54" s="3">
         <v>4500</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4935,8 +5064,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4971,106 +5101,110 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E57" s="3">
         <v>200</v>
       </c>
       <c r="F57" s="3">
+        <v>200</v>
+      </c>
+      <c r="G57" s="3">
         <v>500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3">
-        <v>100</v>
-      </c>
       <c r="I57" s="3">
+        <v>100</v>
+      </c>
+      <c r="J57" s="3">
         <v>700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3">
-        <v>100</v>
-      </c>
       <c r="N57" s="3">
+        <v>100</v>
+      </c>
+      <c r="O57" s="3">
         <v>800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>200</v>
-      </c>
-      <c r="R57" s="3">
-        <v>300</v>
       </c>
       <c r="S57" s="3">
         <v>300</v>
       </c>
       <c r="T57" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="U57" s="3">
+        <v>0</v>
+      </c>
+      <c r="V57" s="3">
         <v>200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>400</v>
-      </c>
-      <c r="W57" s="3">
-        <v>600</v>
       </c>
       <c r="X57" s="3">
         <v>600</v>
       </c>
       <c r="Y57" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z57" s="3">
         <v>400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>900</v>
-      </c>
-      <c r="AG57" s="3">
-        <v>1100</v>
       </c>
       <c r="AH57" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5102,7 +5236,7 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N58" s="3">
         <v>200</v>
@@ -5111,19 +5245,19 @@
         <v>200</v>
       </c>
       <c r="P58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q58" s="3">
         <v>100</v>
       </c>
-      <c r="R58" s="3" t="s">
+      <c r="R58" s="3">
+        <v>100</v>
+      </c>
+      <c r="S58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="S58" s="3">
-        <v>100</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>24</v>
+      <c r="T58" s="3">
+        <v>100</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>24</v>
@@ -5137,8 +5271,8 @@
       <c r="X58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -5167,8 +5301,11 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5176,31 +5313,31 @@
         <v>400</v>
       </c>
       <c r="E59" s="3">
+        <v>400</v>
+      </c>
+      <c r="F59" s="3">
         <v>500</v>
-      </c>
-      <c r="F59" s="3">
-        <v>300</v>
       </c>
       <c r="G59" s="3">
         <v>300</v>
       </c>
       <c r="H59" s="3">
+        <v>300</v>
+      </c>
+      <c r="I59" s="3">
         <v>400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>500</v>
-      </c>
-      <c r="M59" s="3">
-        <v>400</v>
       </c>
       <c r="N59" s="3">
         <v>400</v>
@@ -5209,25 +5346,25 @@
         <v>400</v>
       </c>
       <c r="P59" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q59" s="3">
         <v>500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>700</v>
-      </c>
-      <c r="R59" s="3">
-        <v>300</v>
       </c>
       <c r="S59" s="3">
         <v>300</v>
       </c>
       <c r="T59" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="U59" s="3">
         <v>400</v>
       </c>
       <c r="V59" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="W59" s="3">
         <v>300</v>
@@ -5239,132 +5376,138 @@
         <v>300</v>
       </c>
       <c r="Z59" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA59" s="3">
         <v>200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>500</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>600</v>
       </c>
       <c r="AD59" s="3">
         <v>600</v>
       </c>
       <c r="AE59" s="3">
+        <v>600</v>
+      </c>
+      <c r="AF59" s="3">
         <v>500</v>
-      </c>
-      <c r="AF59" s="3">
-        <v>400</v>
       </c>
       <c r="AG59" s="3">
         <v>400</v>
       </c>
       <c r="AH59" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI59" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>400</v>
+      </c>
+      <c r="E60" s="3">
         <v>600</v>
-      </c>
-      <c r="E60" s="3">
-        <v>800</v>
       </c>
       <c r="F60" s="3">
         <v>800</v>
       </c>
       <c r="G60" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="H60" s="3">
         <v>500</v>
       </c>
       <c r="I60" s="3">
+        <v>500</v>
+      </c>
+      <c r="J60" s="3">
         <v>1300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1000</v>
-      </c>
-      <c r="R60" s="3">
-        <v>700</v>
       </c>
       <c r="S60" s="3">
         <v>700</v>
       </c>
       <c r="T60" s="3">
+        <v>700</v>
+      </c>
+      <c r="U60" s="3">
         <v>400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>800</v>
-      </c>
-      <c r="W60" s="3">
-        <v>900</v>
       </c>
       <c r="X60" s="3">
         <v>900</v>
       </c>
       <c r="Y60" s="3">
+        <v>900</v>
+      </c>
+      <c r="Z60" s="3">
         <v>600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5399,7 +5542,7 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="O61" s="3">
         <v>500</v>
@@ -5408,16 +5551,16 @@
         <v>500</v>
       </c>
       <c r="Q61" s="3">
+        <v>500</v>
+      </c>
+      <c r="R61" s="3">
         <v>600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>600</v>
-      </c>
-      <c r="T61" s="3">
-        <v>500</v>
       </c>
       <c r="U61" s="3">
         <v>500</v>
@@ -5461,8 +5604,11 @@
       <c r="AH61" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5479,28 +5625,28 @@
         <v>0</v>
       </c>
       <c r="H62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I62" s="3">
         <v>100</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
       </c>
       <c r="L62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M62" s="3">
         <v>100</v>
       </c>
       <c r="N62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P62" s="3">
         <v>100</v>
@@ -5518,7 +5664,7 @@
         <v>100</v>
       </c>
       <c r="U62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V62" s="3">
         <v>200</v>
@@ -5529,8 +5675,8 @@
       <c r="X62" s="3">
         <v>200</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>24</v>
+      <c r="Y62" s="3">
+        <v>200</v>
       </c>
       <c r="Z62" s="3" t="s">
         <v>24</v>
@@ -5541,8 +5687,8 @@
       <c r="AB62" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC62" s="3">
-        <v>0</v>
+      <c r="AC62" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AD62" s="3">
         <v>0</v>
@@ -5559,8 +5705,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5657,8 +5806,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5755,8 +5907,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5853,106 +6008,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>400</v>
+      </c>
+      <c r="E66" s="3">
         <v>700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>900</v>
-      </c>
-      <c r="G66" s="3">
-        <v>600</v>
       </c>
       <c r="H66" s="3">
         <v>600</v>
       </c>
       <c r="I66" s="3">
+        <v>600</v>
+      </c>
+      <c r="J66" s="3">
         <v>1400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1700</v>
-      </c>
-      <c r="R66" s="3">
-        <v>1400</v>
       </c>
       <c r="S66" s="3">
         <v>1400</v>
       </c>
       <c r="T66" s="3">
+        <v>1400</v>
+      </c>
+      <c r="U66" s="3">
         <v>1000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1400</v>
-      </c>
-      <c r="W66" s="3">
-        <v>1600</v>
       </c>
       <c r="X66" s="3">
         <v>1600</v>
       </c>
       <c r="Y66" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Z66" s="3">
         <v>1100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1900</v>
-      </c>
-      <c r="AG66" s="3">
-        <v>2100</v>
       </c>
       <c r="AH66" s="3">
         <v>2100</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5987,8 +6148,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6085,8 +6247,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6183,8 +6348,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6281,8 +6449,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6379,8 +6550,11 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6388,61 +6562,61 @@
         <v>3100</v>
       </c>
       <c r="E72" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F72" s="3">
         <v>3400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4300</v>
-      </c>
-      <c r="P72" s="3">
-        <v>4200</v>
       </c>
       <c r="Q72" s="3">
         <v>4200</v>
       </c>
       <c r="R72" s="3">
+        <v>4200</v>
+      </c>
+      <c r="S72" s="3">
         <v>4000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3800</v>
-      </c>
-      <c r="T72" s="3">
-        <v>3600</v>
       </c>
       <c r="U72" s="3">
         <v>3600</v>
       </c>
       <c r="V72" s="3">
+        <v>3600</v>
+      </c>
+      <c r="W72" s="3">
         <v>3400</v>
-      </c>
-      <c r="W72" s="3">
-        <v>3500</v>
       </c>
       <c r="X72" s="3">
         <v>3500</v>
@@ -6451,34 +6625,37 @@
         <v>3500</v>
       </c>
       <c r="Z72" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AA72" s="3">
         <v>3300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>3400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>3300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>3000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6575,8 +6752,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6673,8 +6853,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6771,8 +6954,11 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -6780,97 +6966,100 @@
         <v>3500</v>
       </c>
       <c r="E76" s="3">
-        <v>3800</v>
+        <v>3500</v>
       </c>
       <c r="F76" s="3">
         <v>3800</v>
       </c>
       <c r="G76" s="3">
+        <v>3800</v>
+      </c>
+      <c r="H76" s="3">
         <v>3700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4700</v>
-      </c>
-      <c r="O76" s="3">
-        <v>4500</v>
       </c>
       <c r="P76" s="3">
         <v>4500</v>
       </c>
       <c r="Q76" s="3">
+        <v>4500</v>
+      </c>
+      <c r="R76" s="3">
         <v>4400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3800</v>
-      </c>
-      <c r="V76" s="3">
-        <v>3700</v>
       </c>
       <c r="W76" s="3">
         <v>3700</v>
       </c>
       <c r="X76" s="3">
-        <v>3800</v>
+        <v>3700</v>
       </c>
       <c r="Y76" s="3">
         <v>3800</v>
       </c>
       <c r="Z76" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AA76" s="3">
         <v>3600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6967,188 +7156,194 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E80" s="2">
         <v>45381</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45290</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45108</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45017</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44835</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44744</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44653</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44562</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44471</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44380</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44289</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44198</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44100</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44009</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43918</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43827</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43736</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43645</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43554</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43463</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43372</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43099</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42917</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42826</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3">
         <v>-300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-100</v>
       </c>
-      <c r="F81" s="3">
-        <v>100</v>
-      </c>
       <c r="G81" s="3">
+        <v>100</v>
+      </c>
+      <c r="H81" s="3">
         <v>-300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-300</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-200</v>
       </c>
       <c r="K81" s="3">
         <v>-200</v>
       </c>
       <c r="L81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M81" s="3">
         <v>200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-100</v>
       </c>
-      <c r="N81" s="3">
-        <v>100</v>
-      </c>
       <c r="O81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q81" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R81" s="3">
         <v>200</v>
       </c>
       <c r="S81" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T81" s="3">
         <v>100</v>
       </c>
       <c r="U81" s="3">
+        <v>100</v>
+      </c>
+      <c r="V81" s="3">
         <v>200</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
       <c r="W81" s="3">
+        <v>0</v>
+      </c>
+      <c r="X81" s="3">
         <v>-100</v>
       </c>
-      <c r="X81" s="3">
-        <v>0</v>
-      </c>
       <c r="Y81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="3">
         <v>200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-100</v>
       </c>
-      <c r="AA81" s="3">
-        <v>100</v>
-      </c>
       <c r="AB81" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AC81" s="3">
         <v>300</v>
@@ -7160,16 +7355,19 @@
         <v>300</v>
       </c>
       <c r="AF81" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG81" s="3">
         <v>-200</v>
       </c>
-      <c r="AG81" s="3">
-        <v>100</v>
-      </c>
       <c r="AH81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7204,8 +7402,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7302,8 +7501,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7400,8 +7602,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7498,8 +7703,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7596,8 +7804,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7694,8 +7905,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7792,74 +8006,77 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-500</v>
       </c>
-      <c r="E89" s="3">
-        <v>100</v>
-      </c>
       <c r="F89" s="3">
         <v>100</v>
       </c>
       <c r="G89" s="3">
+        <v>100</v>
+      </c>
+      <c r="H89" s="3">
         <v>200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-700</v>
       </c>
-      <c r="I89" s="3">
-        <v>100</v>
-      </c>
       <c r="J89" s="3">
+        <v>100</v>
+      </c>
+      <c r="K89" s="3">
         <v>-200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1000</v>
       </c>
-      <c r="Q89" s="3">
-        <v>100</v>
-      </c>
       <c r="R89" s="3">
+        <v>100</v>
+      </c>
+      <c r="S89" s="3">
         <v>300</v>
       </c>
-      <c r="S89" s="3">
-        <v>100</v>
-      </c>
       <c r="T89" s="3">
+        <v>100</v>
+      </c>
+      <c r="U89" s="3">
         <v>400</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
       <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3">
         <v>-400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>300</v>
       </c>
-      <c r="X89" s="3">
-        <v>100</v>
-      </c>
       <c r="Y89" s="3">
         <v>100</v>
       </c>
@@ -7867,31 +8084,34 @@
         <v>100</v>
       </c>
       <c r="AA89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>200</v>
       </c>
-      <c r="AE89" s="3">
-        <v>100</v>
-      </c>
       <c r="AF89" s="3">
         <v>100</v>
       </c>
       <c r="AG89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH89" s="3">
         <v>-100</v>
       </c>
-      <c r="AH89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7926,8 +8146,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8024,8 +8245,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8122,8 +8346,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8220,8 +8447,11 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8291,8 +8521,8 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>24</v>
+      <c r="Z94" s="3">
+        <v>0</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>24</v>
@@ -8300,8 +8530,8 @@
       <c r="AB94" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
+      <c r="AC94" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AD94" s="3">
         <v>0</v>
@@ -8318,8 +8548,11 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8354,8 +8587,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8452,8 +8686,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8550,8 +8787,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8648,8 +8888,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8746,8 +8989,11 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8766,8 +9012,8 @@
       <c r="H100" s="3">
         <v>0</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>24</v>
+      <c r="I100" s="3">
+        <v>0</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>24</v>
@@ -8778,11 +9024,11 @@
       <c r="L100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N100" s="3">
         <v>-500</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>24</v>
@@ -8790,18 +9036,18 @@
       <c r="P100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
+      <c r="Q100" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
-      <c r="S100" s="3" t="s">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
@@ -8844,8 +9090,11 @@
       <c r="AH100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8942,102 +9191,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-500</v>
       </c>
-      <c r="E102" s="3">
-        <v>100</v>
-      </c>
       <c r="F102" s="3">
         <v>100</v>
       </c>
       <c r="G102" s="3">
+        <v>100</v>
+      </c>
+      <c r="H102" s="3">
         <v>200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-700</v>
       </c>
-      <c r="I102" s="3">
-        <v>100</v>
-      </c>
       <c r="J102" s="3">
+        <v>100</v>
+      </c>
+      <c r="K102" s="3">
         <v>-200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1000</v>
       </c>
-      <c r="Q102" s="3">
-        <v>100</v>
-      </c>
       <c r="R102" s="3">
+        <v>100</v>
+      </c>
+      <c r="S102" s="3">
         <v>300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>400</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>-400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>300</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
       <c r="Y102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>200</v>
       </c>
-      <c r="AE102" s="3">
-        <v>100</v>
-      </c>
       <c r="AF102" s="3">
         <v>100</v>
       </c>
       <c r="AG102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH102" s="3">
         <v>-100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>
